--- a/groo 산출물/groo 요구사항정의서.xlsx
+++ b/groo 산출물/groo 요구사항정의서.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="1652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="1677">
   <si>
     <t>요구사항정의서</t>
   </si>
@@ -13489,6 +13489,141 @@
 스터디 관리 - 새 페이지 열기
 </t>
   </si>
+  <si>
+    <t>아이디와 비밀번호를 찾을 수 있는 방법이 있어야 한다.</t>
+  </si>
+  <si>
+    <t>회원가입을 할 수 있어야 한다. -로그인페이지</t>
+  </si>
+  <si>
+    <t>취소를 선택하면 로그인 화면으로 이동해야 한다. -이용약관 페이지</t>
+  </si>
+  <si>
+    <t>필수 항목이 존재해야 한다.</t>
+  </si>
+  <si>
+    <t>일반회원은 아이디, 비밀번호, 이름, 주민번호 앞 6자리, 뒷자리 1자리, 이메일을 반드시 입력 받아야 한다.</t>
+  </si>
+  <si>
+    <t>회원가입이 완료됐음을 알려주고 확인을 누르면 메인페이지로 이동한다. - 회원가입페이지</t>
+  </si>
+  <si>
+    <t>비회원이 로그인을 누르면 로그인 페이지로 이동해야 한다. 
+* AJAX 방식으로 페이지 구현 * 
+ - 아이디
+ - 패스워드
+비밀번호 찾기, 회원가입, 아이디 찾기
+ㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡ
+소셜 로그인
+- 카카오 구글 네이버
+ㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡㅡ</t>
+  </si>
+  <si>
+    <t>문의하기를 누르면 관리자와 1:1대화창이 열려야 한다. 비회원은 회원가입 페이지 - 메인페이지</t>
+  </si>
+  <si>
+    <t>문의하기를 누르면 관리자와 1:1대화창이 열려야 한다. 비회원은 회원가입 페이지 -회원 상세페이지</t>
+  </si>
+  <si>
+    <t>문의하기를 누르면 관리자와 1:1대화창이 열려야 한다. 비회원은 회원가입 페이지 -마이 페이지</t>
+  </si>
+  <si>
+    <t>들어갈때 비번 입력하는거 
+새로운 페이지를 만든다 : 기존방법유지
+새로운 페이지를 만들지 않을거다 : 들어간 후 비밀번호를 입력하지 않으면 수정못하는 방법 - 회원상세페이지</t>
+  </si>
+  <si>
+    <t>문의하기를 누르면 관리자와 1:1대화창이 열려야 한다. 비회원은 회원가입 페이지 - 게시판 페이지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">좌측 Nav가 있어야한다.
+*ajax, include 방식으로 구현*
+스터디 생성
+- 스터디 타이틀이 있어야 한다.
+- 스터디 장이 있어야 한다.
+- 스터디 카테고리를 설정할 수 있어야 한다.
+- 스터디 비밀번호를 설정할 수 있어야 한다. (선택)
+- 스터디 기간이 있어야 한다.
+- 스터디 카테고리를 설정할 수 있어야 한다.
+- 스터디 소개 글을 쓸 수 있어야 한다.
+- 자세한 스터디 내용을 쓸 수 있어야 한다.
+스터디 보기
+- 진행하고 있는 스터디의 타이틀을 확인할 수 있어야 한다.
+- 진행하고 있는 스터디의 팀원수를 조회할 수 있어야 한다.
+- 진행하고 있는 스터디의 좋아요 수를 확인 할 수 있어야 한다.
+- 진행하고 있는 스터드의 찜를 확인 할 수 있어야 한다.
+- 진행하고 있는 스터디의 장을 확인 할 수 있어야 한다.
+- 진행하고 있는 스터디에 대해 신고를 할 수 있어야 한다.
+- 진행하고 있는 스터디를 탈퇴 할 수 있어야 한다.
+- 해당 스터디를 누르면 스터디상세보기로 이동한다.
+ ㄴ 스터디 상세보기
+     해당 스터디의 프로필 사진을 확인할 수 있어야 한다.
+     해당 스터디의 타이틀을 확인할 수 있어야 한다.
+     해당 스터디의 반장을 확인할 수 있어야 한다.
+     해당 스터디의 팀원들을 조회할 수 있어야 한다.
+     해당 스터디의 팀원들의 직책을 조회할 수 있어야 한다.
+     해당 스터디의 좋아요 수를 확인 할 수 있어야 한다.
+     해당 스터디의 생성일을 확인 할 수 있어야 한다.
+     해당 스터디의 일정표를 확인 할 수 있어야 한다.
+     해당 스터디의 주제 투표를 확인 할 수 있어야 한다.
+     해당 스터디의 소개글을 볼 수 있어야 한다.
+     해당 스터디의 자세한 내용을 볼 수 있어야 한다.
+     해당 스터디의 카테고리를 확인 할 수 있어야 한다.
+     해당 스터디의 실시간채팅 기능을 이용 할 수 있어야 한다.
+     해당 스터디의 사용하는 원격 사이트에 대해 링크를 제공해야 한다.
+ ㄴ 스터디 게시물
+     해당 스터디의 관련된 게시물 목록을 보여준다.
+스터디 관리 - 새 페이지 열기
+</t>
+  </si>
+  <si>
+    <t>회원탈퇴를 할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>스터디의 카테고리를 확인, 등록, 수정, 삭제할 수 있어야 한다. -스터다 관리 페이지</t>
+  </si>
+  <si>
+    <t>스터디의 카테고리를 확인, 등록, 수정, 삭제할 수 있어야 한다. -스터다 관리 
+페이지</t>
+  </si>
+  <si>
+    <t>입력 사항 미기재 시 미입력 사항이 있다는 경고창을 띄운다. - 게시물</t>
+  </si>
+  <si>
+    <t>대시보드는 월별 가입자 수를 보여줘야 한다. -통계 페이지</t>
+  </si>
+  <si>
+    <t>사용자 관리 게시판은 엑셀로 출력할 수 있어야 한다. - 대시보드</t>
+  </si>
+  <si>
+    <t>스터디 관리 게시판은 활성되고 있는 스터디를 보여줘야 한다.</t>
+  </si>
+  <si>
+    <t>스터디 관리 게시판은 신규스터디를 보여줘야 한다.</t>
+  </si>
+  <si>
+    <t>스터디 관리 게시판은 비활성화된 스터디를 보여줘야 한다.</t>
+  </si>
+  <si>
+    <t>비활성화가 된 스터디가 다시 활성화가 될 수 있게 해야 한다. - 스터디 관리 페이지</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">통계 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+      </rPr>
+      <t>페이지</t>
+    </r>
+  </si>
+  <si>
+    <t>사용자 관리 게시판은 엑셀로 출력할 수 있어야 한다. - 사용자 관리 페이지</t>
+  </si>
 </sst>
 </file>
 
@@ -13505,7 +13640,7 @@
     <numFmt numFmtId="182" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="183" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="69">
+  <fonts count="70">
     <font>
       <sz val="11.0"/>
       <name val="맑은 고딕"/>
@@ -13908,8 +14043,14 @@
       <name val="宋体"/>
       <color theme="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12.0"/>
+      <name val="돋움"/>
+      <color theme="1"/>
+    </font>
   </fonts>
-  <fills count="39">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -14135,12 +14276,6 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="27">
     <border>
@@ -14845,7 +14980,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="656">
+  <cellXfs count="657">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -16724,25 +16859,25 @@
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="38" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="37" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="38" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="60" fillId="37" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="38" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="37" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="38" borderId="6" xfId="20" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="37" borderId="6" xfId="20" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="38" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="37" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="38" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="37" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="38" borderId="0" xfId="20" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="37" borderId="0" xfId="20" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="60" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -16813,6 +16948,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="141">
@@ -17249,7 +17387,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U512"/>
+  <dimension ref="A1:U513"/>
   <sheetFormatPr defaultColWidth="9.00000000" defaultRowHeight="16.500000"/>
   <cols>
     <col min="1" max="1" style="311" width="22.87999916" customWidth="1" outlineLevel="0"/>
@@ -17403,7 +17541,7 @@
       <c r="B6" s="437"/>
       <c r="C6" s="437"/>
       <c r="D6" s="28" t="s">
-        <v>1017</v>
+        <v>1652</v>
       </c>
       <c r="E6" s="434" t="s">
         <v>24</v>
@@ -17420,17 +17558,21 @@
       <c r="M6" s="459"/>
       <c r="O6" s="460"/>
     </row>
-    <row r="7" spans="1:15" ht="17.250000" customHeight="1">
+    <row r="7" spans="1:15">
       <c r="A7" s="437"/>
-      <c r="B7" s="437"/>
-      <c r="C7" s="437"/>
+      <c r="B7" s="437" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" s="437" t="s">
+        <v>1102</v>
+      </c>
       <c r="D7" s="28" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="E7" s="434" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="434"/>
+      <c r="F7" s="437"/>
       <c r="G7" s="434" t="s">
         <v>170</v>
       </c>
@@ -17438,35 +17580,31 @@
       <c r="I7" s="434"/>
       <c r="J7" s="434"/>
       <c r="K7" s="434"/>
-      <c r="L7" s="434"/>
+      <c r="L7" s="483">
+        <v>1</v>
+      </c>
       <c r="M7" s="459"/>
       <c r="O7" s="460"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" ht="17.250000" customHeight="1">
       <c r="A8" s="437"/>
-      <c r="B8" s="437" t="s">
-        <v>214</v>
-      </c>
-      <c r="C8" s="437" t="s">
-        <v>1102</v>
-      </c>
+      <c r="B8" s="437"/>
+      <c r="C8" s="437"/>
       <c r="D8" s="28" t="s">
-        <v>1117</v>
+        <v>1653</v>
       </c>
       <c r="E8" s="434" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="295"/>
+      <c r="F8" s="434"/>
       <c r="G8" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="H8" s="295"/>
-      <c r="I8" s="295"/>
-      <c r="J8" s="295"/>
-      <c r="K8" s="295"/>
-      <c r="L8" s="483">
-        <v>1</v>
-      </c>
+      <c r="H8" s="434"/>
+      <c r="I8" s="434"/>
+      <c r="J8" s="434"/>
+      <c r="K8" s="434"/>
+      <c r="L8" s="434"/>
       <c r="M8" s="459"/>
       <c r="O8" s="460"/>
     </row>
@@ -17474,8 +17612,8 @@
       <c r="A9" s="437"/>
       <c r="B9" s="437"/>
       <c r="C9" s="437"/>
-      <c r="D9" s="295" t="s">
-        <v>1118</v>
+      <c r="D9" s="28" t="s">
+        <v>1117</v>
       </c>
       <c r="E9" s="434" t="s">
         <v>24</v>
@@ -17497,7 +17635,7 @@
       <c r="B10" s="437"/>
       <c r="C10" s="437"/>
       <c r="D10" s="295" t="s">
-        <v>1119</v>
+        <v>1655</v>
       </c>
       <c r="E10" s="434" t="s">
         <v>24</v>
@@ -17519,7 +17657,7 @@
       <c r="B11" s="437"/>
       <c r="C11" s="437"/>
       <c r="D11" s="295" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="E11" s="434" t="s">
         <v>24</v>
@@ -17536,7 +17674,7 @@
       <c r="M11" s="459"/>
       <c r="O11" s="460"/>
     </row>
-    <row r="12" spans="1:15" ht="17.250000" customHeight="1">
+    <row r="12" spans="1:15" ht="28.500000" customHeight="1">
       <c r="A12" s="437"/>
       <c r="B12" s="437"/>
       <c r="C12" s="437"/>
@@ -17560,10 +17698,14 @@
     </row>
     <row r="13" spans="1:15" ht="28.500000" customHeight="1">
       <c r="A13" s="437"/>
-      <c r="B13" s="437"/>
-      <c r="C13" s="437"/>
+      <c r="B13" s="437" t="s">
+        <v>278</v>
+      </c>
+      <c r="C13" s="437" t="s">
+        <v>436</v>
+      </c>
       <c r="D13" s="295" t="s">
-        <v>1122</v>
+        <v>1654</v>
       </c>
       <c r="E13" s="434" t="s">
         <v>24</v>
@@ -17576,20 +17718,18 @@
       <c r="I13" s="295"/>
       <c r="J13" s="295"/>
       <c r="K13" s="295"/>
-      <c r="L13" s="434"/>
+      <c r="L13" s="483">
+        <v>1</v>
+      </c>
       <c r="M13" s="459"/>
       <c r="O13" s="460"/>
     </row>
-    <row r="14" spans="1:15" ht="28.500000" customHeight="1">
+    <row r="14" spans="1:15" ht="28.500000">
       <c r="A14" s="437"/>
-      <c r="B14" s="437" t="s">
-        <v>278</v>
-      </c>
-      <c r="C14" s="437" t="s">
-        <v>436</v>
-      </c>
+      <c r="B14" s="437"/>
+      <c r="C14" s="437"/>
       <c r="D14" s="295" t="s">
-        <v>1147</v>
+        <v>1656</v>
       </c>
       <c r="E14" s="434" t="s">
         <v>24</v>
@@ -17602,11 +17742,9 @@
       <c r="I14" s="295"/>
       <c r="J14" s="295"/>
       <c r="K14" s="295"/>
-      <c r="L14" s="483">
-        <v>1</v>
-      </c>
+      <c r="L14" s="434"/>
       <c r="M14" s="459"/>
-      <c r="O14" s="460"/>
+      <c r="N14" s="459"/>
     </row>
     <row r="15" spans="1:15" ht="17.250000" customHeight="1">
       <c r="A15" s="437"/>
@@ -17628,7 +17766,8 @@
       <c r="K15" s="434"/>
       <c r="L15" s="434"/>
       <c r="M15" s="459"/>
-      <c r="N15" s="459"/>
+      <c r="N15" s="166"/>
+      <c r="O15" s="166"/>
     </row>
     <row r="16" spans="1:15" ht="17.250000" customHeight="1">
       <c r="A16" s="437"/>
@@ -17770,8 +17909,12 @@
     </row>
     <row r="22" spans="1:15" ht="17.250000" customHeight="1">
       <c r="A22" s="437"/>
-      <c r="B22" s="437"/>
-      <c r="C22" s="437"/>
+      <c r="B22" s="437" t="s">
+        <v>279</v>
+      </c>
+      <c r="C22" s="437" t="s">
+        <v>1123</v>
+      </c>
       <c r="D22" s="295" t="s">
         <v>804</v>
       </c>
@@ -17786,18 +17929,20 @@
       <c r="I22" s="434"/>
       <c r="J22" s="434"/>
       <c r="K22" s="434"/>
-      <c r="L22" s="434"/>
+      <c r="L22" s="483">
+        <v>1</v>
+      </c>
       <c r="M22" s="459"/>
       <c r="N22" s="166"/>
       <c r="O22" s="166"/>
     </row>
-    <row r="23" spans="1:15" ht="17.250000" customHeight="1">
+    <row r="23" spans="1:15">
       <c r="A23" s="437"/>
       <c r="B23" s="437" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C23" s="437" t="s">
-        <v>1123</v>
+        <v>1152</v>
       </c>
       <c r="D23" s="295" t="s">
         <v>350</v>
@@ -17813,23 +17958,19 @@
       <c r="I23" s="434"/>
       <c r="J23" s="434"/>
       <c r="K23" s="434"/>
-      <c r="L23" s="483">
-        <v>1</v>
+      <c r="L23" s="495">
+        <v>0.7</v>
       </c>
       <c r="M23" s="459"/>
       <c r="N23" s="166"/>
       <c r="O23" s="166"/>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" ht="42.750000">
       <c r="A24" s="437"/>
-      <c r="B24" s="437" t="s">
-        <v>284</v>
-      </c>
-      <c r="C24" s="437" t="s">
-        <v>1152</v>
-      </c>
+      <c r="B24" s="437"/>
+      <c r="C24" s="438"/>
       <c r="D24" s="295" t="s">
-        <v>1124</v>
+        <v>1657</v>
       </c>
       <c r="E24" s="434" t="s">
         <v>24</v>
@@ -17842,9 +17983,7 @@
       <c r="I24" s="434"/>
       <c r="J24" s="434"/>
       <c r="K24" s="434"/>
-      <c r="L24" s="495">
-        <v>0.7</v>
-      </c>
+      <c r="L24" s="437"/>
       <c r="M24" s="459"/>
       <c r="N24" s="166"/>
       <c r="O24" s="166"/>
@@ -17876,7 +18015,7 @@
       <c r="N25" s="166"/>
       <c r="O25" s="166"/>
     </row>
-    <row r="26" spans="1:15" ht="17.250000" customHeight="1">
+    <row r="26" spans="1:15">
       <c r="A26" s="437"/>
       <c r="B26" s="437"/>
       <c r="C26" s="438"/>
@@ -17899,7 +18038,7 @@
       <c r="N26" s="166"/>
       <c r="O26" s="166"/>
     </row>
-    <row r="27" spans="1:15" ht="17.250000" customHeight="1">
+    <row r="27" spans="1:15">
       <c r="A27" s="437"/>
       <c r="B27" s="437"/>
       <c r="C27" s="438"/>
@@ -17964,16 +18103,16 @@
       <c r="J29" s="434"/>
       <c r="K29" s="434"/>
       <c r="L29" s="437"/>
-      <c r="M29" s="459"/>
+      <c r="M29" s="151"/>
       <c r="N29" s="166"/>
       <c r="O29" s="166"/>
     </row>
-    <row r="30" spans="1:15" ht="142.500000">
+    <row r="30" spans="1:15" ht="128.250000">
       <c r="A30" s="437"/>
       <c r="B30" s="437"/>
       <c r="C30" s="438"/>
       <c r="D30" s="30" t="s">
-        <v>1237</v>
+        <v>1658</v>
       </c>
       <c r="E30" s="434" t="s">
         <v>24</v>
@@ -17987,7 +18126,7 @@
       <c r="J30" s="434"/>
       <c r="K30" s="434"/>
       <c r="L30" s="437"/>
-      <c r="M30" s="151"/>
+      <c r="M30" s="311"/>
       <c r="N30" s="166"/>
       <c r="O30" s="166"/>
     </row>
@@ -18010,7 +18149,7 @@
       <c r="J31" s="434"/>
       <c r="K31" s="434"/>
       <c r="L31" s="437"/>
-      <c r="M31" s="311"/>
+      <c r="M31" s="151"/>
       <c r="N31" s="166"/>
       <c r="O31" s="166"/>
     </row>
@@ -18037,7 +18176,7 @@
       <c r="N32" s="166"/>
       <c r="O32" s="166"/>
     </row>
-    <row r="33" spans="1:15" ht="28.500000" customHeight="1">
+    <row r="33" spans="1:15" ht="28.500000">
       <c r="A33" s="437"/>
       <c r="B33" s="437"/>
       <c r="C33" s="438"/>
@@ -18058,7 +18197,7 @@
       <c r="J33" s="434"/>
       <c r="K33" s="434"/>
       <c r="L33" s="437"/>
-      <c r="M33" s="151"/>
+      <c r="M33" s="311"/>
       <c r="N33" s="166"/>
       <c r="O33" s="166"/>
     </row>
@@ -18083,14 +18222,14 @@
       <c r="J34" s="434"/>
       <c r="K34" s="434"/>
       <c r="L34" s="437"/>
-      <c r="M34" s="311"/>
+      <c r="M34" s="151"/>
       <c r="N34" s="166"/>
       <c r="O34" s="166"/>
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="437"/>
-      <c r="B35" s="437"/>
-      <c r="C35" s="438"/>
+      <c r="B35" s="434"/>
+      <c r="C35" s="434"/>
       <c r="D35" s="295" t="s">
         <v>1201</v>
       </c>
@@ -18107,15 +18246,19 @@
       <c r="I35" s="434"/>
       <c r="J35" s="434"/>
       <c r="K35" s="434"/>
-      <c r="L35" s="437"/>
-      <c r="M35" s="151"/>
+      <c r="L35" s="434"/>
+      <c r="M35" s="311"/>
       <c r="N35" s="166"/>
       <c r="O35" s="166"/>
     </row>
     <row r="36" spans="1:15" ht="28.500000">
       <c r="A36" s="437"/>
-      <c r="B36" s="434"/>
-      <c r="C36" s="434"/>
+      <c r="B36" s="437" t="s">
+        <v>291</v>
+      </c>
+      <c r="C36" s="438" t="s">
+        <v>151</v>
+      </c>
       <c r="D36" s="295" t="s">
         <v>1168</v>
       </c>
@@ -18132,21 +18275,19 @@
       <c r="I36" s="295"/>
       <c r="J36" s="295"/>
       <c r="K36" s="295"/>
-      <c r="L36" s="434"/>
-      <c r="M36" s="311"/>
+      <c r="L36" s="495">
+        <v>0.5</v>
+      </c>
+      <c r="M36" s="151"/>
       <c r="N36" s="166"/>
       <c r="O36" s="166"/>
     </row>
-    <row r="37" spans="1:15" ht="17.250000" customHeight="1">
+    <row r="37" spans="1:15" ht="28.500000">
       <c r="A37" s="437"/>
-      <c r="B37" s="437" t="s">
-        <v>291</v>
-      </c>
-      <c r="C37" s="438" t="s">
-        <v>151</v>
-      </c>
+      <c r="B37" s="437"/>
+      <c r="C37" s="437"/>
       <c r="D37" s="295" t="s">
-        <v>1277</v>
+        <v>1659</v>
       </c>
       <c r="E37" s="434" t="s">
         <v>24</v>
@@ -18159,17 +18300,15 @@
       <c r="I37" s="434"/>
       <c r="J37" s="434"/>
       <c r="K37" s="434"/>
-      <c r="L37" s="495">
-        <v>0.5</v>
-      </c>
-      <c r="M37" s="151"/>
+      <c r="L37" s="437"/>
+      <c r="M37" s="311"/>
       <c r="N37" s="166"/>
       <c r="O37" s="166"/>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" s="437"/>
       <c r="B38" s="437"/>
-      <c r="C38" s="437"/>
+      <c r="C38" s="438"/>
       <c r="D38" s="295" t="s">
         <v>1202</v>
       </c>
@@ -18185,7 +18324,7 @@
       <c r="J38" s="434"/>
       <c r="K38" s="434"/>
       <c r="L38" s="437"/>
-      <c r="M38" s="311"/>
+      <c r="M38" s="459"/>
       <c r="N38" s="166"/>
       <c r="O38" s="166"/>
     </row>
@@ -18207,15 +18346,21 @@
       <c r="I39" s="434"/>
       <c r="J39" s="434"/>
       <c r="K39" s="434"/>
-      <c r="L39" s="437"/>
+      <c r="L39" s="495">
+        <v>0.6</v>
+      </c>
       <c r="M39" s="459"/>
       <c r="N39" s="166"/>
       <c r="O39" s="166"/>
     </row>
     <row r="40" spans="1:15" ht="327.750000">
       <c r="A40" s="437"/>
-      <c r="B40" s="437"/>
-      <c r="C40" s="438"/>
+      <c r="B40" s="437" t="s">
+        <v>292</v>
+      </c>
+      <c r="C40" s="438" t="s">
+        <v>824</v>
+      </c>
       <c r="D40" s="295" t="s">
         <v>1228</v>
       </c>
@@ -18230,23 +18375,17 @@
       <c r="I40" s="434"/>
       <c r="J40" s="434"/>
       <c r="K40" s="434"/>
-      <c r="L40" s="495">
-        <v>0.6</v>
-      </c>
+      <c r="L40" s="437"/>
       <c r="M40" s="459"/>
       <c r="N40" s="166"/>
       <c r="O40" s="166"/>
     </row>
     <row r="41" spans="1:15" ht="17.250000" customHeight="1">
       <c r="A41" s="437"/>
-      <c r="B41" s="437" t="s">
-        <v>292</v>
-      </c>
-      <c r="C41" s="438" t="s">
-        <v>824</v>
-      </c>
+      <c r="B41" s="437"/>
+      <c r="C41" s="438"/>
       <c r="D41" s="295" t="s">
-        <v>1277</v>
+        <v>1661</v>
       </c>
       <c r="E41" s="434" t="s">
         <v>24</v>
@@ -18471,7 +18610,7 @@
       <c r="N50" s="166"/>
       <c r="O50" s="166"/>
     </row>
-    <row r="51" spans="1:21" ht="17.250000" customHeight="1">
+    <row r="51" spans="1:21">
       <c r="A51" s="437"/>
       <c r="B51" s="437"/>
       <c r="C51" s="438"/>
@@ -18496,37 +18635,32 @@
     </row>
     <row r="52" spans="1:21">
       <c r="A52" s="437"/>
-      <c r="B52" s="437"/>
-      <c r="C52" s="438"/>
-      <c r="D52" s="295" t="s">
-        <v>1250</v>
-      </c>
-      <c r="E52" s="434" t="s">
-        <v>24</v>
-      </c>
-      <c r="F52" s="434" t="s">
-        <v>170</v>
-      </c>
+      <c r="B52" s="437" t="s">
+        <v>301</v>
+      </c>
+      <c r="C52" s="438" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D52" s="28" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E52" s="434"/>
+      <c r="F52" s="434"/>
       <c r="G52" s="434"/>
       <c r="H52" s="434"/>
       <c r="I52" s="434"/>
       <c r="J52" s="434"/>
       <c r="K52" s="434"/>
-      <c r="L52" s="437"/>
-      <c r="M52" s="459"/>
-      <c r="N52" s="166"/>
-      <c r="O52" s="166"/>
-    </row>
-    <row r="53" spans="1:21" ht="57.000000" customHeight="1">
+      <c r="L52" s="495">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21">
       <c r="A53" s="437"/>
-      <c r="B53" s="437" t="s">
-        <v>292</v>
-      </c>
-      <c r="C53" s="438" t="s">
-        <v>1261</v>
-      </c>
-      <c r="D53" s="28" t="s">
-        <v>1252</v>
+      <c r="B53" s="437"/>
+      <c r="C53" s="438"/>
+      <c r="D53" s="295" t="s">
+        <v>1250</v>
       </c>
       <c r="E53" s="434" t="s">
         <v>24</v>
@@ -18539,17 +18673,14 @@
       <c r="I53" s="434"/>
       <c r="J53" s="434"/>
       <c r="K53" s="434"/>
-      <c r="L53" s="495">
-        <v>0.6</v>
-      </c>
-      <c r="M53" s="460"/>
-    </row>
-    <row r="54" spans="1:21">
+      <c r="L53" s="495"/>
+    </row>
+    <row r="54" spans="1:21" ht="57.000000">
       <c r="A54" s="437"/>
       <c r="B54" s="437"/>
       <c r="C54" s="438"/>
-      <c r="D54" s="295" t="s">
-        <v>1202</v>
+      <c r="D54" s="28" t="s">
+        <v>1662</v>
       </c>
       <c r="E54" s="434" t="s">
         <v>24</v>
@@ -18562,15 +18693,14 @@
       <c r="I54" s="434"/>
       <c r="J54" s="434"/>
       <c r="K54" s="434"/>
-      <c r="L54" s="495"/>
-      <c r="M54" s="460"/>
-    </row>
-    <row r="55" spans="1:21" ht="270.750000" customHeight="1">
+      <c r="L54" s="437"/>
+    </row>
+    <row r="55" spans="1:21">
       <c r="A55" s="437"/>
       <c r="B55" s="437"/>
       <c r="C55" s="438"/>
-      <c r="D55" s="28" t="s">
-        <v>1323</v>
+      <c r="D55" s="295" t="s">
+        <v>1202</v>
       </c>
       <c r="E55" s="434" t="s">
         <v>24</v>
@@ -18583,15 +18713,20 @@
       <c r="I55" s="434"/>
       <c r="J55" s="434"/>
       <c r="K55" s="434"/>
-      <c r="L55" s="437"/>
-      <c r="M55" s="460"/>
-    </row>
-    <row r="56" spans="1:21" ht="17.250000" customHeight="1">
-      <c r="A56" s="437"/>
-      <c r="B56" s="437"/>
-      <c r="C56" s="438"/>
-      <c r="D56" s="295" t="s">
-        <v>1280</v>
+      <c r="L55" s="434"/>
+    </row>
+    <row r="56" spans="1:21" ht="28.500000" customHeight="1">
+      <c r="A56" s="437" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B56" s="437" t="s">
+        <v>331</v>
+      </c>
+      <c r="C56" s="438" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D56" s="28" t="s">
+        <v>1323</v>
       </c>
       <c r="E56" s="434" t="s">
         <v>24</v>
@@ -18605,20 +18740,13 @@
       <c r="J56" s="434"/>
       <c r="K56" s="434"/>
       <c r="L56" s="434"/>
-      <c r="M56" s="460"/>
-    </row>
-    <row r="57" spans="1:21" ht="28.500000" customHeight="1">
-      <c r="A57" s="437" t="s">
-        <v>1428</v>
-      </c>
-      <c r="B57" s="437" t="s">
-        <v>331</v>
-      </c>
-      <c r="C57" s="438" t="s">
-        <v>1292</v>
-      </c>
-      <c r="D57" s="296" t="s">
-        <v>1277</v>
+    </row>
+    <row r="57" spans="1:21">
+      <c r="A57" s="437"/>
+      <c r="B57" s="437"/>
+      <c r="C57" s="437"/>
+      <c r="D57" s="295" t="s">
+        <v>1280</v>
       </c>
       <c r="E57" s="434" t="s">
         <v>24</v>
@@ -18631,20 +18759,21 @@
       <c r="I57" s="434"/>
       <c r="J57" s="434"/>
       <c r="K57" s="434"/>
-      <c r="L57" s="434"/>
-      <c r="M57" s="460"/>
-    </row>
-    <row r="58" spans="1:21">
+      <c r="L57" s="640">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" ht="17.250000" customHeight="1">
       <c r="A58" s="437"/>
       <c r="B58" s="437"/>
       <c r="C58" s="437"/>
-      <c r="D58" s="295" t="s">
-        <v>1202</v>
+      <c r="D58" s="296" t="s">
+        <v>1663</v>
       </c>
       <c r="E58" s="434" t="s">
         <v>24</v>
       </c>
-      <c r="F58" s="437" t="s">
+      <c r="F58" s="434" t="s">
         <v>170</v>
       </c>
       <c r="G58" s="434"/>
@@ -18652,17 +18781,14 @@
       <c r="I58" s="434"/>
       <c r="J58" s="434"/>
       <c r="K58" s="434"/>
-      <c r="L58" s="640">
-        <v>0.6</v>
-      </c>
-      <c r="M58" s="460"/>
+      <c r="L58" s="95"/>
     </row>
     <row r="59" spans="1:21" ht="17.250000" customHeight="1">
       <c r="A59" s="437"/>
       <c r="B59" s="437"/>
       <c r="C59" s="437"/>
-      <c r="D59" s="647" t="s">
-        <v>1651</v>
+      <c r="D59" s="295" t="s">
+        <v>1202</v>
       </c>
       <c r="E59" s="434" t="s">
         <v>24</v>
@@ -18674,24 +18800,36 @@
       <c r="H59" s="434"/>
       <c r="I59" s="434"/>
       <c r="J59" s="434"/>
-      <c r="K59" s="437"/>
+      <c r="K59" s="434"/>
       <c r="L59" s="95"/>
-      <c r="M59" s="460"/>
+      <c r="N59" s="311"/>
+      <c r="O59" s="463"/>
+      <c r="P59" s="463"/>
+      <c r="Q59" s="463"/>
+      <c r="R59" s="463"/>
+      <c r="S59" s="463"/>
+      <c r="T59" s="463"/>
+      <c r="U59" s="463"/>
     </row>
     <row r="60" spans="1:21" ht="17.250000" customHeight="1">
       <c r="A60" s="437"/>
       <c r="B60" s="437"/>
       <c r="C60" s="437"/>
-      <c r="D60" s="502"/>
-      <c r="E60" s="434"/>
-      <c r="F60" s="437"/>
+      <c r="D60" s="647" t="s">
+        <v>1664</v>
+      </c>
+      <c r="E60" s="434" t="s">
+        <v>24</v>
+      </c>
+      <c r="F60" s="437" t="s">
+        <v>170</v>
+      </c>
       <c r="G60" s="434"/>
       <c r="H60" s="434"/>
       <c r="I60" s="434"/>
       <c r="J60" s="434"/>
       <c r="K60" s="437"/>
       <c r="L60" s="95"/>
-      <c r="M60" s="460"/>
       <c r="N60" s="311"/>
       <c r="O60" s="463"/>
       <c r="P60" s="463"/>
@@ -18714,7 +18852,6 @@
       <c r="J61" s="434"/>
       <c r="K61" s="437"/>
       <c r="L61" s="95"/>
-      <c r="M61" s="460"/>
       <c r="N61" s="311"/>
       <c r="O61" s="463"/>
       <c r="P61" s="463"/>
@@ -18724,7 +18861,7 @@
       <c r="T61" s="463"/>
       <c r="U61" s="463"/>
     </row>
-    <row r="62" spans="1:21" ht="17.250000" customHeight="1">
+    <row r="62" spans="1:21">
       <c r="A62" s="437"/>
       <c r="B62" s="437"/>
       <c r="C62" s="437"/>
@@ -18737,7 +18874,6 @@
       <c r="J62" s="434"/>
       <c r="K62" s="437"/>
       <c r="L62" s="95"/>
-      <c r="M62" s="460"/>
       <c r="N62" s="311"/>
       <c r="O62" s="463"/>
       <c r="P62" s="463"/>
@@ -18747,7 +18883,7 @@
       <c r="T62" s="463"/>
       <c r="U62" s="463"/>
     </row>
-    <row r="63" spans="1:21">
+    <row r="63" spans="1:21" ht="255.250000" customHeight="1">
       <c r="A63" s="437"/>
       <c r="B63" s="437"/>
       <c r="C63" s="437"/>
@@ -18760,7 +18896,6 @@
       <c r="J63" s="434"/>
       <c r="K63" s="437"/>
       <c r="L63" s="95"/>
-      <c r="M63" s="460"/>
       <c r="N63" s="311"/>
       <c r="O63" s="463"/>
       <c r="P63" s="463"/>
@@ -18770,7 +18905,7 @@
       <c r="T63" s="463"/>
       <c r="U63" s="463"/>
     </row>
-    <row r="64" spans="1:21" ht="255.250000" customHeight="1">
+    <row r="64" spans="1:21" ht="16.500000" hidden="1" customHeight="1">
       <c r="A64" s="437"/>
       <c r="B64" s="437"/>
       <c r="C64" s="437"/>
@@ -18783,7 +18918,6 @@
       <c r="J64" s="434"/>
       <c r="K64" s="437"/>
       <c r="L64" s="95"/>
-      <c r="M64" s="460"/>
       <c r="N64" s="311"/>
       <c r="O64" s="463"/>
       <c r="P64" s="463"/>
@@ -18793,7 +18927,7 @@
       <c r="T64" s="463"/>
       <c r="U64" s="463"/>
     </row>
-    <row r="65" spans="1:21" ht="16.500000" hidden="1" customHeight="1">
+    <row r="65" spans="1:21" ht="221.600000" customHeight="1">
       <c r="A65" s="437"/>
       <c r="B65" s="437"/>
       <c r="C65" s="437"/>
@@ -18805,8 +18939,7 @@
       <c r="I65" s="434"/>
       <c r="J65" s="434"/>
       <c r="K65" s="437"/>
-      <c r="L65" s="95"/>
-      <c r="M65" s="460"/>
+      <c r="L65" s="641"/>
       <c r="N65" s="311"/>
       <c r="O65" s="463"/>
       <c r="P65" s="463"/>
@@ -18816,11 +18949,15 @@
       <c r="T65" s="463"/>
       <c r="U65" s="463"/>
     </row>
-    <row r="66" spans="1:21" ht="221.600000" customHeight="1">
+    <row r="66" spans="1:21" ht="17.250000" customHeight="1">
       <c r="A66" s="437"/>
-      <c r="B66" s="437"/>
-      <c r="C66" s="437"/>
-      <c r="D66" s="648"/>
+      <c r="B66" s="437" t="s">
+        <v>332</v>
+      </c>
+      <c r="C66" s="437" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D66" s="502"/>
       <c r="E66" s="434"/>
       <c r="F66" s="437"/>
       <c r="G66" s="434"/>
@@ -18828,8 +18965,7 @@
       <c r="I66" s="434"/>
       <c r="J66" s="434"/>
       <c r="K66" s="437"/>
-      <c r="L66" s="641"/>
-      <c r="M66" s="460"/>
+      <c r="L66" s="296"/>
       <c r="N66" s="311"/>
       <c r="O66" s="463"/>
       <c r="P66" s="463"/>
@@ -18841,28 +18977,18 @@
     </row>
     <row r="67" spans="1:21" ht="17.250000" customHeight="1">
       <c r="A67" s="437"/>
-      <c r="B67" s="437" t="s">
-        <v>332</v>
-      </c>
-      <c r="C67" s="437" t="s">
-        <v>1433</v>
-      </c>
-      <c r="D67" s="295" t="s">
-        <v>1395</v>
-      </c>
-      <c r="E67" s="434" t="s">
-        <v>24</v>
-      </c>
-      <c r="F67" s="434" t="s">
-        <v>170</v>
-      </c>
-      <c r="G67" s="295"/>
-      <c r="H67" s="295"/>
-      <c r="I67" s="295"/>
-      <c r="J67" s="295"/>
-      <c r="K67" s="296"/>
+      <c r="B67" s="437"/>
+      <c r="C67" s="437"/>
+      <c r="D67" s="648"/>
+      <c r="E67" s="434"/>
+      <c r="F67" s="437"/>
+      <c r="G67" s="434"/>
+      <c r="H67" s="434"/>
+      <c r="I67" s="434"/>
+      <c r="J67" s="434"/>
+      <c r="K67" s="437"/>
       <c r="L67" s="296"/>
-      <c r="M67" s="460"/>
+      <c r="M67" s="161"/>
       <c r="N67" s="311"/>
       <c r="O67" s="463"/>
       <c r="P67" s="463"/>
@@ -18872,12 +18998,12 @@
       <c r="T67" s="463"/>
       <c r="U67" s="463"/>
     </row>
-    <row r="68" spans="1:21" ht="17.250000" customHeight="1">
+    <row r="68" spans="1:21">
       <c r="A68" s="437"/>
       <c r="B68" s="437"/>
       <c r="C68" s="437"/>
       <c r="D68" s="295" t="s">
-        <v>1381</v>
+        <v>1395</v>
       </c>
       <c r="E68" s="434" t="s">
         <v>24</v>
@@ -18889,10 +19015,10 @@
       <c r="H68" s="295"/>
       <c r="I68" s="295"/>
       <c r="J68" s="295"/>
-      <c r="K68" s="295"/>
+      <c r="K68" s="296"/>
       <c r="L68" s="296"/>
       <c r="M68" s="161"/>
-      <c r="N68" s="311"/>
+      <c r="N68" s="161"/>
       <c r="O68" s="463"/>
       <c r="P68" s="463"/>
       <c r="Q68" s="463"/>
@@ -18901,12 +19027,12 @@
       <c r="T68" s="463"/>
       <c r="U68" s="463"/>
     </row>
-    <row r="69" spans="1:21">
+    <row r="69" spans="1:21" ht="28.500000">
       <c r="A69" s="437"/>
       <c r="B69" s="437"/>
       <c r="C69" s="437"/>
       <c r="D69" s="295" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="E69" s="434" t="s">
         <v>24</v>
@@ -18930,12 +19056,12 @@
       <c r="T69" s="463"/>
       <c r="U69" s="463"/>
     </row>
-    <row r="70" spans="1:21" ht="28.500000">
+    <row r="70" spans="1:21">
       <c r="A70" s="437"/>
       <c r="B70" s="437"/>
       <c r="C70" s="437"/>
       <c r="D70" s="295" t="s">
-        <v>1374</v>
+        <v>1382</v>
       </c>
       <c r="E70" s="434" t="s">
         <v>24</v>
@@ -18950,7 +19076,7 @@
       <c r="K70" s="295"/>
       <c r="L70" s="296"/>
       <c r="M70" s="161"/>
-      <c r="N70" s="161"/>
+      <c r="N70" s="311"/>
       <c r="O70" s="463"/>
       <c r="P70" s="463"/>
       <c r="Q70" s="463"/>
@@ -18959,12 +19085,12 @@
       <c r="T70" s="463"/>
       <c r="U70" s="463"/>
     </row>
-    <row r="71" spans="1:21" ht="17.250000" customHeight="1">
+    <row r="71" spans="1:21" ht="28.500000">
       <c r="A71" s="437"/>
       <c r="B71" s="437"/>
       <c r="C71" s="437"/>
       <c r="D71" s="295" t="s">
-        <v>1380</v>
+        <v>1374</v>
       </c>
       <c r="E71" s="434" t="s">
         <v>24</v>
@@ -18979,7 +19105,7 @@
       <c r="K71" s="295"/>
       <c r="L71" s="296"/>
       <c r="M71" s="161"/>
-      <c r="N71" s="311"/>
+      <c r="N71" s="161"/>
       <c r="O71" s="463"/>
       <c r="P71" s="463"/>
       <c r="Q71" s="463"/>
@@ -18988,12 +19114,12 @@
       <c r="T71" s="463"/>
       <c r="U71" s="463"/>
     </row>
-    <row r="72" spans="1:21" ht="17.250000" customHeight="1">
+    <row r="72" spans="1:21">
       <c r="A72" s="437"/>
       <c r="B72" s="437"/>
       <c r="C72" s="437"/>
       <c r="D72" s="295" t="s">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="E72" s="434" t="s">
         <v>24</v>
@@ -19007,7 +19133,7 @@
       <c r="J72" s="295"/>
       <c r="K72" s="295"/>
       <c r="L72" s="296"/>
-      <c r="M72" s="161"/>
+      <c r="M72" s="464"/>
       <c r="N72" s="161"/>
       <c r="O72" s="463"/>
       <c r="P72" s="463"/>
@@ -19022,7 +19148,7 @@
       <c r="B73" s="437"/>
       <c r="C73" s="437"/>
       <c r="D73" s="295" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="E73" s="434" t="s">
         <v>24</v>
@@ -19046,12 +19172,12 @@
       <c r="T73" s="463"/>
       <c r="U73" s="463"/>
     </row>
-    <row r="74" spans="1:21">
+    <row r="74" spans="1:21" ht="28.500000" customHeight="1">
       <c r="A74" s="437"/>
       <c r="B74" s="437"/>
       <c r="C74" s="437"/>
       <c r="D74" s="295" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="E74" s="434" t="s">
         <v>24</v>
@@ -19065,7 +19191,7 @@
       <c r="J74" s="295"/>
       <c r="K74" s="295"/>
       <c r="L74" s="296"/>
-      <c r="M74" s="464"/>
+      <c r="M74" s="161"/>
       <c r="N74" s="161"/>
       <c r="O74" s="463"/>
       <c r="P74" s="463"/>
@@ -19075,12 +19201,12 @@
       <c r="T74" s="463"/>
       <c r="U74" s="463"/>
     </row>
-    <row r="75" spans="1:21" ht="28.500000" customHeight="1">
+    <row r="75" spans="1:21" ht="17.250000" customHeight="1">
       <c r="A75" s="437"/>
       <c r="B75" s="437"/>
       <c r="C75" s="437"/>
       <c r="D75" s="295" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="E75" s="434" t="s">
         <v>24</v>
@@ -19094,8 +19220,8 @@
       <c r="J75" s="295"/>
       <c r="K75" s="295"/>
       <c r="L75" s="296"/>
-      <c r="M75" s="161"/>
-      <c r="N75" s="161"/>
+      <c r="M75" s="464"/>
+      <c r="N75" s="311"/>
       <c r="O75" s="463"/>
       <c r="P75" s="463"/>
       <c r="Q75" s="463"/>
@@ -19109,7 +19235,7 @@
       <c r="B76" s="437"/>
       <c r="C76" s="437"/>
       <c r="D76" s="295" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="E76" s="434" t="s">
         <v>24</v>
@@ -19138,7 +19264,7 @@
       <c r="B77" s="437"/>
       <c r="C77" s="437"/>
       <c r="D77" s="295" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="E77" s="434" t="s">
         <v>24</v>
@@ -19153,21 +19279,27 @@
       <c r="K77" s="295"/>
       <c r="L77" s="296"/>
       <c r="M77" s="464"/>
-      <c r="N77" s="311"/>
+      <c r="N77" s="161"/>
       <c r="O77" s="463"/>
-      <c r="P77" s="463"/>
-      <c r="Q77" s="463"/>
+      <c r="P77" s="311"/>
+      <c r="Q77" s="311"/>
       <c r="R77" s="463"/>
-      <c r="S77" s="463"/>
-      <c r="T77" s="463"/>
+      <c r="S77" s="311"/>
+      <c r="T77" s="311"/>
       <c r="U77" s="463"/>
     </row>
-    <row r="78" spans="1:21" ht="17.250000" customHeight="1">
-      <c r="A78" s="437"/>
-      <c r="B78" s="437"/>
-      <c r="C78" s="437"/>
+    <row r="78" spans="1:21" ht="28.500000" customHeight="1">
+      <c r="A78" s="437" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B78" s="434" t="s">
+        <v>344</v>
+      </c>
+      <c r="C78" s="438" t="s">
+        <v>1092</v>
+      </c>
       <c r="D78" s="295" t="s">
-        <v>1519</v>
+        <v>1393</v>
       </c>
       <c r="E78" s="434" t="s">
         <v>24</v>
@@ -19180,29 +19312,24 @@
       <c r="I78" s="295"/>
       <c r="J78" s="295"/>
       <c r="K78" s="295"/>
-      <c r="L78" s="296"/>
-      <c r="M78" s="464"/>
-      <c r="N78" s="161"/>
-      <c r="O78" s="463"/>
-      <c r="P78" s="311"/>
-      <c r="Q78" s="311"/>
-      <c r="R78" s="463"/>
-      <c r="S78" s="311"/>
-      <c r="T78" s="311"/>
-      <c r="U78" s="463"/>
+      <c r="L78" s="495">
+        <v>0.5</v>
+      </c>
+      <c r="N78" s="459"/>
+      <c r="O78" s="459"/>
+      <c r="P78" s="460"/>
+      <c r="Q78" s="460"/>
+      <c r="R78" s="460"/>
+      <c r="S78" s="460"/>
+      <c r="T78" s="460"/>
+      <c r="U78" s="460"/>
     </row>
     <row r="79" spans="1:21" ht="28.500000" customHeight="1">
-      <c r="A79" s="437" t="s">
-        <v>1429</v>
-      </c>
-      <c r="B79" s="434" t="s">
-        <v>344</v>
-      </c>
-      <c r="C79" s="438" t="s">
-        <v>1092</v>
-      </c>
+      <c r="A79" s="437"/>
+      <c r="B79" s="434"/>
+      <c r="C79" s="438"/>
       <c r="D79" s="295" t="s">
-        <v>1394</v>
+        <v>1519</v>
       </c>
       <c r="E79" s="434" t="s">
         <v>24</v>
@@ -19210,23 +19337,20 @@
       <c r="F79" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="G79" s="434"/>
-      <c r="H79" s="434"/>
-      <c r="I79" s="434"/>
-      <c r="J79" s="434"/>
-      <c r="K79" s="434"/>
-      <c r="L79" s="495">
-        <v>0.5</v>
-      </c>
-      <c r="M79" s="460"/>
+      <c r="G79" s="295"/>
+      <c r="H79" s="295"/>
+      <c r="I79" s="295"/>
+      <c r="J79" s="295"/>
+      <c r="K79" s="295"/>
+      <c r="L79" s="495"/>
       <c r="N79" s="459"/>
     </row>
-    <row r="80" spans="1:21" ht="28.500000" customHeight="1">
+    <row r="80" spans="1:21" ht="17.250000" customHeight="1">
       <c r="A80" s="437"/>
       <c r="B80" s="434"/>
       <c r="C80" s="438"/>
-      <c r="D80" s="103" t="s">
-        <v>1093</v>
+      <c r="D80" s="295" t="s">
+        <v>1667</v>
       </c>
       <c r="E80" s="434" t="s">
         <v>24</v>
@@ -19239,16 +19363,21 @@
       <c r="I80" s="434"/>
       <c r="J80" s="434"/>
       <c r="K80" s="434"/>
-      <c r="L80" s="495"/>
-      <c r="M80" s="460"/>
+      <c r="L80" s="437"/>
       <c r="N80" s="459"/>
     </row>
-    <row r="81" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A81" s="437"/>
-      <c r="B81" s="434"/>
-      <c r="C81" s="438"/>
+    <row r="81" spans="1:14" ht="28.500000">
+      <c r="A81" s="437" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B81" s="434" t="s">
+        <v>336</v>
+      </c>
+      <c r="C81" s="434" t="s">
+        <v>1432</v>
+      </c>
       <c r="D81" s="103" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E81" s="434" t="s">
         <v>24</v>
@@ -19261,22 +19390,17 @@
       <c r="I81" s="434"/>
       <c r="J81" s="434"/>
       <c r="K81" s="434"/>
-      <c r="L81" s="437"/>
-      <c r="M81" s="460"/>
+      <c r="L81" s="495">
+        <v>0.3</v>
+      </c>
       <c r="N81" s="459"/>
     </row>
     <row r="82" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A82" s="437" t="s">
-        <v>1430</v>
-      </c>
-      <c r="B82" s="434" t="s">
-        <v>336</v>
-      </c>
-      <c r="C82" s="434" t="s">
-        <v>1432</v>
-      </c>
+      <c r="A82" s="437"/>
+      <c r="B82" s="434"/>
+      <c r="C82" s="434"/>
       <c r="D82" s="103" t="s">
-        <v>350</v>
+        <v>1095</v>
       </c>
       <c r="E82" s="434" t="s">
         <v>24</v>
@@ -19289,32 +19413,28 @@
       <c r="I82" s="434"/>
       <c r="J82" s="434"/>
       <c r="K82" s="434"/>
-      <c r="L82" s="495">
-        <v>0.3</v>
-      </c>
-      <c r="M82" s="460"/>
+      <c r="L82" s="437"/>
       <c r="N82" s="459"/>
     </row>
     <row r="83" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A83" s="437"/>
       <c r="B83" s="434"/>
       <c r="C83" s="434"/>
-      <c r="D83" s="295" t="s">
-        <v>934</v>
+      <c r="D83" s="103" t="s">
+        <v>1668</v>
       </c>
       <c r="E83" s="434" t="s">
         <v>24</v>
       </c>
-      <c r="F83" s="434"/>
+      <c r="F83" s="434" t="s">
+        <v>170</v>
+      </c>
       <c r="G83" s="434"/>
       <c r="H83" s="434"/>
       <c r="I83" s="434"/>
       <c r="J83" s="434"/>
-      <c r="K83" s="434" t="s">
-        <v>170</v>
-      </c>
+      <c r="K83" s="434"/>
       <c r="L83" s="437"/>
-      <c r="M83" s="460"/>
       <c r="N83" s="459"/>
     </row>
     <row r="84" spans="1:14" ht="17.250000" customHeight="1">
@@ -19322,7 +19442,7 @@
       <c r="B84" s="434"/>
       <c r="C84" s="434"/>
       <c r="D84" s="295" t="s">
-        <v>749</v>
+        <v>934</v>
       </c>
       <c r="E84" s="434" t="s">
         <v>24</v>
@@ -19336,15 +19456,18 @@
         <v>170</v>
       </c>
       <c r="L84" s="437"/>
-      <c r="M84" s="460"/>
       <c r="N84" s="459"/>
     </row>
     <row r="85" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A85" s="437"/>
-      <c r="B85" s="434"/>
-      <c r="C85" s="434"/>
+      <c r="B85" s="434" t="s">
+        <v>339</v>
+      </c>
+      <c r="C85" s="434" t="s">
+        <v>1425</v>
+      </c>
       <c r="D85" s="295" t="s">
-        <v>935</v>
+        <v>749</v>
       </c>
       <c r="E85" s="434" t="s">
         <v>24</v>
@@ -19358,19 +19481,14 @@
         <v>170</v>
       </c>
       <c r="L85" s="437"/>
-      <c r="M85" s="460"/>
       <c r="N85" s="459"/>
     </row>
     <row r="86" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A86" s="437"/>
-      <c r="B86" s="434" t="s">
-        <v>339</v>
-      </c>
-      <c r="C86" s="434" t="s">
-        <v>1425</v>
-      </c>
+      <c r="B86" s="434"/>
+      <c r="C86" s="434"/>
       <c r="D86" s="295" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="E86" s="434" t="s">
         <v>24</v>
@@ -19384,7 +19502,6 @@
         <v>170</v>
       </c>
       <c r="L86" s="437"/>
-      <c r="M86" s="460"/>
       <c r="N86" s="459"/>
     </row>
     <row r="87" spans="1:14" ht="17.250000" customHeight="1">
@@ -19392,7 +19509,7 @@
       <c r="B87" s="434"/>
       <c r="C87" s="434"/>
       <c r="D87" s="295" t="s">
-        <v>937</v>
+        <v>1669</v>
       </c>
       <c r="E87" s="434" t="s">
         <v>24</v>
@@ -19406,7 +19523,6 @@
         <v>170</v>
       </c>
       <c r="L87" s="437"/>
-      <c r="M87" s="460"/>
       <c r="N87" s="459"/>
     </row>
     <row r="88" spans="1:14" ht="17.250000" customHeight="1">
@@ -19414,7 +19530,7 @@
       <c r="B88" s="434"/>
       <c r="C88" s="434"/>
       <c r="D88" s="295" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="E88" s="434" t="s">
         <v>24</v>
@@ -19428,7 +19544,6 @@
         <v>170</v>
       </c>
       <c r="L88" s="437"/>
-      <c r="M88" s="460"/>
       <c r="N88" s="459"/>
     </row>
     <row r="89" spans="1:14" ht="17.250000" customHeight="1">
@@ -19436,7 +19551,7 @@
       <c r="B89" s="434"/>
       <c r="C89" s="434"/>
       <c r="D89" s="295" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E89" s="434" t="s">
         <v>24</v>
@@ -19450,7 +19565,6 @@
         <v>170</v>
       </c>
       <c r="L89" s="437"/>
-      <c r="M89" s="460"/>
       <c r="N89" s="459"/>
     </row>
     <row r="90" spans="1:14" ht="17.250000" customHeight="1">
@@ -19458,7 +19572,7 @@
       <c r="B90" s="434"/>
       <c r="C90" s="434"/>
       <c r="D90" s="295" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E90" s="434" t="s">
         <v>24</v>
@@ -19472,7 +19586,6 @@
         <v>170</v>
       </c>
       <c r="L90" s="437"/>
-      <c r="M90" s="460"/>
       <c r="N90" s="459"/>
     </row>
     <row r="91" spans="1:14" ht="17.250000" customHeight="1">
@@ -19480,7 +19593,7 @@
       <c r="B91" s="434"/>
       <c r="C91" s="434"/>
       <c r="D91" s="295" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="E91" s="434" t="s">
         <v>24</v>
@@ -19494,7 +19607,6 @@
         <v>170</v>
       </c>
       <c r="L91" s="437"/>
-      <c r="M91" s="460"/>
       <c r="N91" s="459"/>
     </row>
     <row r="92" spans="1:14" ht="17.250000" customHeight="1">
@@ -19502,7 +19614,7 @@
       <c r="B92" s="434"/>
       <c r="C92" s="434"/>
       <c r="D92" s="295" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="E92" s="434" t="s">
         <v>24</v>
@@ -19516,7 +19628,6 @@
         <v>170</v>
       </c>
       <c r="L92" s="437"/>
-      <c r="M92" s="460"/>
       <c r="N92" s="459"/>
     </row>
     <row r="93" spans="1:14" ht="17.250000" customHeight="1">
@@ -19524,7 +19635,7 @@
       <c r="B93" s="434"/>
       <c r="C93" s="434"/>
       <c r="D93" s="295" t="s">
-        <v>801</v>
+        <v>942</v>
       </c>
       <c r="E93" s="434" t="s">
         <v>24</v>
@@ -19538,7 +19649,6 @@
         <v>170</v>
       </c>
       <c r="L93" s="437"/>
-      <c r="M93" s="460"/>
       <c r="N93" s="459"/>
     </row>
     <row r="94" spans="1:14" ht="17.250000" customHeight="1">
@@ -19546,7 +19656,7 @@
       <c r="B94" s="434"/>
       <c r="C94" s="434"/>
       <c r="D94" s="295" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="E94" s="434" t="s">
         <v>24</v>
@@ -19560,7 +19670,6 @@
         <v>170</v>
       </c>
       <c r="L94" s="437"/>
-      <c r="M94" s="460"/>
       <c r="N94" s="459"/>
     </row>
     <row r="95" spans="1:14" ht="17.250000" customHeight="1">
@@ -19568,7 +19677,7 @@
       <c r="B95" s="434"/>
       <c r="C95" s="434"/>
       <c r="D95" s="295" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="E95" s="434" t="s">
         <v>24</v>
@@ -19582,15 +19691,18 @@
         <v>170</v>
       </c>
       <c r="L95" s="437"/>
-      <c r="M95" s="460"/>
       <c r="N95" s="459"/>
     </row>
     <row r="96" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A96" s="437"/>
-      <c r="B96" s="434"/>
-      <c r="C96" s="434"/>
+      <c r="B96" s="434" t="s">
+        <v>344</v>
+      </c>
+      <c r="C96" s="434" t="s">
+        <v>1433</v>
+      </c>
       <c r="D96" s="295" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E96" s="434" t="s">
         <v>24</v>
@@ -19604,19 +19716,14 @@
         <v>170</v>
       </c>
       <c r="L96" s="437"/>
-      <c r="M96" s="460"/>
       <c r="N96" s="459"/>
     </row>
     <row r="97" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A97" s="437"/>
-      <c r="B97" s="434" t="s">
-        <v>344</v>
-      </c>
-      <c r="C97" s="434" t="s">
-        <v>1433</v>
-      </c>
+      <c r="B97" s="434"/>
+      <c r="C97" s="434"/>
       <c r="D97" s="295" t="s">
-        <v>1000</v>
+        <v>806</v>
       </c>
       <c r="E97" s="434" t="s">
         <v>24</v>
@@ -19630,7 +19737,6 @@
         <v>170</v>
       </c>
       <c r="L97" s="437"/>
-      <c r="M97" s="460"/>
       <c r="N97" s="459"/>
     </row>
     <row r="98" spans="1:14" ht="17.250000" customHeight="1">
@@ -19638,7 +19744,7 @@
       <c r="B98" s="434"/>
       <c r="C98" s="434"/>
       <c r="D98" s="295" t="s">
-        <v>772</v>
+        <v>1676</v>
       </c>
       <c r="E98" s="434" t="s">
         <v>24</v>
@@ -19652,7 +19758,7 @@
         <v>170</v>
       </c>
       <c r="L98" s="437"/>
-      <c r="M98" s="460"/>
+      <c r="M98" s="459"/>
       <c r="N98" s="459"/>
     </row>
     <row r="99" spans="1:14" ht="17.250000" customHeight="1">
@@ -19660,7 +19766,7 @@
       <c r="B99" s="434"/>
       <c r="C99" s="434"/>
       <c r="D99" s="295" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="E99" s="434" t="s">
         <v>24</v>
@@ -19682,7 +19788,7 @@
       <c r="B100" s="434"/>
       <c r="C100" s="434"/>
       <c r="D100" s="295" t="s">
-        <v>780</v>
+        <v>1671</v>
       </c>
       <c r="E100" s="434" t="s">
         <v>24</v>
@@ -19704,7 +19810,7 @@
       <c r="B101" s="434"/>
       <c r="C101" s="434"/>
       <c r="D101" s="295" t="s">
-        <v>781</v>
+        <v>1672</v>
       </c>
       <c r="E101" s="434" t="s">
         <v>24</v>
@@ -19726,7 +19832,7 @@
       <c r="B102" s="434"/>
       <c r="C102" s="434"/>
       <c r="D102" s="295" t="s">
-        <v>466</v>
+        <v>1673</v>
       </c>
       <c r="E102" s="434" t="s">
         <v>24</v>
@@ -19748,7 +19854,7 @@
       <c r="B103" s="434"/>
       <c r="C103" s="434"/>
       <c r="D103" s="295" t="s">
-        <v>808</v>
+        <v>466</v>
       </c>
       <c r="E103" s="434" t="s">
         <v>24</v>
@@ -19762,15 +19868,14 @@
         <v>170</v>
       </c>
       <c r="L103" s="437"/>
-      <c r="M103" s="459"/>
-      <c r="N103" s="459"/>
+      <c r="N103" s="460"/>
     </row>
     <row r="104" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A104" s="437"/>
       <c r="B104" s="434"/>
       <c r="C104" s="434"/>
       <c r="D104" s="295" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E104" s="434" t="s">
         <v>24</v>
@@ -19784,15 +19889,13 @@
         <v>170</v>
       </c>
       <c r="L104" s="437"/>
-      <c r="M104" s="460"/>
-      <c r="N104" s="460"/>
     </row>
     <row r="105" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A105" s="437"/>
       <c r="B105" s="434"/>
       <c r="C105" s="434"/>
       <c r="D105" s="295" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E105" s="434" t="s">
         <v>24</v>
@@ -19806,14 +19909,17 @@
         <v>170</v>
       </c>
       <c r="L105" s="437"/>
-      <c r="M105" s="460"/>
     </row>
     <row r="106" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A106" s="437"/>
-      <c r="B106" s="434"/>
-      <c r="C106" s="434"/>
+      <c r="B106" s="434" t="s">
+        <v>344</v>
+      </c>
+      <c r="C106" s="434" t="s">
+        <v>1435</v>
+      </c>
       <c r="D106" s="295" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E106" s="434" t="s">
         <v>24</v>
@@ -19827,18 +19933,13 @@
         <v>170</v>
       </c>
       <c r="L106" s="437"/>
-      <c r="M106" s="460"/>
     </row>
     <row r="107" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A107" s="437"/>
-      <c r="B107" s="434" t="s">
-        <v>344</v>
-      </c>
-      <c r="C107" s="434" t="s">
-        <v>1435</v>
-      </c>
+      <c r="B107" s="434"/>
+      <c r="C107" s="434"/>
       <c r="D107" s="295" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="E107" s="434" t="s">
         <v>24</v>
@@ -19852,14 +19953,13 @@
         <v>170</v>
       </c>
       <c r="L107" s="437"/>
-      <c r="M107" s="460"/>
     </row>
     <row r="108" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A108" s="437"/>
       <c r="B108" s="434"/>
       <c r="C108" s="434"/>
       <c r="D108" s="295" t="s">
-        <v>814</v>
+        <v>1674</v>
       </c>
       <c r="E108" s="434" t="s">
         <v>24</v>
@@ -19873,14 +19973,13 @@
         <v>170</v>
       </c>
       <c r="L108" s="437"/>
-      <c r="M108" s="460"/>
     </row>
     <row r="109" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A109" s="437"/>
       <c r="B109" s="434"/>
       <c r="C109" s="434"/>
       <c r="D109" s="295" t="s">
-        <v>795</v>
+        <v>814</v>
       </c>
       <c r="E109" s="434" t="s">
         <v>24</v>
@@ -19894,14 +19993,13 @@
         <v>170</v>
       </c>
       <c r="L109" s="437"/>
-      <c r="M109" s="460"/>
     </row>
     <row r="110" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A110" s="437"/>
       <c r="B110" s="434"/>
       <c r="C110" s="434"/>
       <c r="D110" s="295" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E110" s="434" t="s">
         <v>24</v>
@@ -19915,14 +20013,13 @@
         <v>170</v>
       </c>
       <c r="L110" s="437"/>
-      <c r="M110" s="460"/>
     </row>
     <row r="111" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A111" s="437"/>
       <c r="B111" s="434"/>
       <c r="C111" s="434"/>
       <c r="D111" s="295" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E111" s="434" t="s">
         <v>24</v>
@@ -19936,14 +20033,13 @@
         <v>170</v>
       </c>
       <c r="L111" s="437"/>
-      <c r="M111" s="460"/>
     </row>
     <row r="112" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A112" s="437"/>
       <c r="B112" s="434"/>
       <c r="C112" s="434"/>
       <c r="D112" s="295" t="s">
-        <v>788</v>
+        <v>797</v>
       </c>
       <c r="E112" s="434" t="s">
         <v>24</v>
@@ -19957,14 +20053,13 @@
         <v>170</v>
       </c>
       <c r="L112" s="437"/>
-      <c r="M112" s="460"/>
     </row>
     <row r="113" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A113" s="437"/>
       <c r="B113" s="434"/>
       <c r="C113" s="434"/>
       <c r="D113" s="295" t="s">
-        <v>815</v>
+        <v>788</v>
       </c>
       <c r="E113" s="434" t="s">
         <v>24</v>
@@ -19978,14 +20073,13 @@
         <v>170</v>
       </c>
       <c r="L113" s="437"/>
-      <c r="M113" s="460"/>
     </row>
     <row r="114" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A114" s="437"/>
       <c r="B114" s="434"/>
       <c r="C114" s="434"/>
       <c r="D114" s="295" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E114" s="434" t="s">
         <v>24</v>
@@ -19999,14 +20093,17 @@
         <v>170</v>
       </c>
       <c r="L114" s="437"/>
-      <c r="M114" s="460"/>
     </row>
     <row r="115" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A115" s="437"/>
-      <c r="B115" s="434"/>
-      <c r="C115" s="434"/>
+      <c r="B115" s="446" t="s">
+        <v>334</v>
+      </c>
+      <c r="C115" s="437" t="s">
+        <v>1434</v>
+      </c>
       <c r="D115" s="295" t="s">
-        <v>976</v>
+        <v>816</v>
       </c>
       <c r="E115" s="434" t="s">
         <v>24</v>
@@ -20020,18 +20117,13 @@
         <v>170</v>
       </c>
       <c r="L115" s="437"/>
-      <c r="M115" s="460"/>
     </row>
     <row r="116" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A116" s="437"/>
-      <c r="B116" s="446" t="s">
-        <v>334</v>
-      </c>
-      <c r="C116" s="437" t="s">
-        <v>1434</v>
-      </c>
+      <c r="B116" s="447"/>
+      <c r="C116" s="437"/>
       <c r="D116" s="295" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="E116" s="434" t="s">
         <v>24</v>
@@ -20045,14 +20137,13 @@
         <v>170</v>
       </c>
       <c r="L116" s="437"/>
-      <c r="M116" s="460"/>
     </row>
     <row r="117" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A117" s="437"/>
       <c r="B117" s="447"/>
       <c r="C117" s="437"/>
       <c r="D117" s="295" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="E117" s="434" t="s">
         <v>24</v>
@@ -20066,14 +20157,13 @@
         <v>170</v>
       </c>
       <c r="L117" s="437"/>
-      <c r="M117" s="460"/>
     </row>
     <row r="118" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A118" s="437"/>
       <c r="B118" s="447"/>
       <c r="C118" s="437"/>
       <c r="D118" s="295" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="E118" s="434" t="s">
         <v>24</v>
@@ -20087,14 +20177,13 @@
         <v>170</v>
       </c>
       <c r="L118" s="437"/>
-      <c r="M118" s="460"/>
     </row>
     <row r="119" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A119" s="437"/>
       <c r="B119" s="447"/>
       <c r="C119" s="437"/>
       <c r="D119" s="295" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="E119" s="434" t="s">
         <v>24</v>
@@ -20108,14 +20197,13 @@
         <v>170</v>
       </c>
       <c r="L119" s="437"/>
-      <c r="M119" s="460"/>
     </row>
     <row r="120" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A120" s="437"/>
       <c r="B120" s="447"/>
       <c r="C120" s="437"/>
       <c r="D120" s="295" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="E120" s="434" t="s">
         <v>24</v>
@@ -20129,14 +20217,13 @@
         <v>170</v>
       </c>
       <c r="L120" s="437"/>
-      <c r="M120" s="460"/>
     </row>
     <row r="121" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A121" s="437"/>
       <c r="B121" s="447"/>
       <c r="C121" s="437"/>
       <c r="D121" s="295" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="E121" s="434" t="s">
         <v>24</v>
@@ -20150,14 +20237,13 @@
         <v>170</v>
       </c>
       <c r="L121" s="437"/>
-      <c r="M121" s="460"/>
     </row>
     <row r="122" spans="1:13" ht="17.250000" customHeight="1">
-      <c r="A122" s="437"/>
-      <c r="B122" s="447"/>
-      <c r="C122" s="437"/>
+      <c r="A122" s="434"/>
+      <c r="B122" s="448"/>
+      <c r="C122" s="434"/>
       <c r="D122" s="295" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E122" s="434" t="s">
         <v>24</v>
@@ -20170,15 +20256,14 @@
       <c r="K122" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L122" s="437"/>
-      <c r="M122" s="460"/>
-    </row>
-    <row r="123" spans="1:13" ht="17.250000" customHeight="1">
-      <c r="A123" s="434"/>
-      <c r="B123" s="448"/>
-      <c r="C123" s="434"/>
+      <c r="L122" s="434"/>
+      <c r="M122" s="463"/>
+    </row>
+    <row r="123" spans="1:13">
+      <c r="A123" s="463"/>
+      <c r="C123" s="463"/>
       <c r="D123" s="295" t="s">
-        <v>999</v>
+        <v>978</v>
       </c>
       <c r="E123" s="434" t="s">
         <v>24</v>
@@ -20191,29 +20276,30 @@
       <c r="K123" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L123" s="434"/>
-      <c r="M123" s="463"/>
+      <c r="L123" s="463"/>
+      <c r="M123" s="460"/>
     </row>
     <row r="124" spans="1:13">
-      <c r="A124" s="463"/>
-      <c r="B124" s="463"/>
-      <c r="C124" s="463"/>
-      <c r="D124" s="311"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
-      <c r="G124" s="463"/>
-      <c r="H124" s="463"/>
-      <c r="I124" s="463"/>
-      <c r="J124" s="463"/>
-      <c r="K124" s="463"/>
+      <c r="A124" s="464"/>
+      <c r="B124" s="464"/>
+      <c r="C124" s="464"/>
+      <c r="D124" s="295" t="s">
+        <v>999</v>
+      </c>
+      <c r="E124" s="434" t="s">
+        <v>24</v>
+      </c>
+      <c r="F124" s="434"/>
+      <c r="G124" s="434"/>
+      <c r="H124" s="434"/>
+      <c r="I124" s="434"/>
+      <c r="J124" s="434"/>
+      <c r="K124" s="434" t="s">
+        <v>170</v>
+      </c>
       <c r="L124" s="463"/>
-      <c r="M124" s="460"/>
-    </row>
-    <row r="125" spans="1:13">
-      <c r="A125" s="464"/>
-      <c r="B125" s="464"/>
-      <c r="C125" s="464"/>
-      <c r="D125" s="464"/>
+    </row>
+    <row r="125" spans="1:13" ht="40.200000" customHeight="1">
       <c r="F125" s="463"/>
       <c r="G125" s="463"/>
       <c r="H125" s="463"/>
@@ -20223,533 +20309,90 @@
       <c r="L125" s="463"/>
     </row>
     <row r="126" spans="1:13" ht="40.200000" customHeight="1">
-      <c r="A126" s="80" t="s">
-        <v>1437</v>
-      </c>
-      <c r="B126" s="80"/>
-      <c r="C126" s="80"/>
-      <c r="D126" s="80"/>
-      <c r="E126" s="484"/>
-      <c r="F126" s="547"/>
-      <c r="G126" s="547"/>
-      <c r="H126" s="547"/>
-      <c r="I126" s="651"/>
-      <c r="J126" s="651"/>
-      <c r="K126" s="651"/>
-      <c r="L126" s="463"/>
+      <c r="D126" s="464"/>
+      <c r="F126" s="463"/>
+      <c r="G126" s="463"/>
+      <c r="H126" s="463"/>
+      <c r="I126" s="463"/>
+      <c r="J126" s="463"/>
+      <c r="K126" s="463"/>
+      <c r="L126" s="442"/>
     </row>
     <row r="127" spans="1:13" ht="40.200000" customHeight="1">
-      <c r="A127" s="80" t="s">
-        <v>19</v>
-      </c>
-      <c r="B127" s="435" t="s">
-        <v>178</v>
-      </c>
-      <c r="C127" s="435"/>
-      <c r="E127" s="80" t="s">
-        <v>1</v>
-      </c>
-      <c r="F127" s="654">
-        <v>45940</v>
-      </c>
-      <c r="G127" s="441"/>
-      <c r="H127" s="441"/>
-      <c r="I127" s="441"/>
-      <c r="J127" s="441"/>
-      <c r="K127" s="492"/>
-      <c r="L127" s="442"/>
-      <c r="M127" s="460"/>
-    </row>
-    <row r="128" spans="1:13" ht="40.200000" customHeight="1">
-      <c r="A128" s="80" t="s">
-        <v>1490</v>
-      </c>
-      <c r="B128" s="484" t="s">
-        <v>3</v>
-      </c>
-      <c r="C128" s="548"/>
-      <c r="D128" s="80" t="s">
-        <v>5</v>
-      </c>
-      <c r="E128" s="466" t="s">
-        <v>1455</v>
-      </c>
-      <c r="F128" s="463"/>
-      <c r="G128" s="467"/>
-      <c r="H128" s="467"/>
-      <c r="I128" s="467"/>
-      <c r="J128" s="467"/>
-      <c r="K128" s="467"/>
+      <c r="L127" s="463"/>
+    </row>
+    <row r="128" spans="1:13" ht="47.700000" customHeight="1">
       <c r="L128" s="463"/>
     </row>
-    <row r="129" spans="1:12" ht="47.700000" customHeight="1">
-      <c r="A129" s="543" t="s">
-        <v>1585</v>
-      </c>
-      <c r="B129" s="441" t="s">
-        <v>1439</v>
-      </c>
-      <c r="C129" s="441"/>
-      <c r="D129" s="543" t="s">
-        <v>1507</v>
-      </c>
-      <c r="E129" s="584" t="s">
-        <v>1489</v>
-      </c>
-      <c r="F129" s="584"/>
-      <c r="G129" s="584"/>
-      <c r="H129" s="584"/>
-      <c r="I129" s="584"/>
-      <c r="J129" s="584"/>
-      <c r="K129" s="584"/>
+    <row r="129" spans="12:12" ht="42.750000">
       <c r="L129" s="463"/>
     </row>
-    <row r="130" spans="1:12" ht="42.750000">
-      <c r="A130" s="442" t="s">
-        <v>1492</v>
-      </c>
-      <c r="B130" s="442" t="s">
-        <v>1462</v>
-      </c>
-      <c r="C130" s="442"/>
-      <c r="D130" s="511" t="s">
-        <v>1502</v>
-      </c>
-      <c r="E130" s="511" t="s">
-        <v>1473</v>
-      </c>
-      <c r="F130" s="511"/>
-      <c r="G130" s="511"/>
-      <c r="H130" s="511"/>
-      <c r="I130" s="511"/>
-      <c r="J130" s="511"/>
-      <c r="K130" s="511"/>
+    <row r="130" spans="12:12" ht="42.750000">
       <c r="L130" s="463"/>
     </row>
-    <row r="131" spans="1:12" ht="42.750000">
-      <c r="A131" s="442" t="s">
-        <v>1475</v>
-      </c>
-      <c r="B131" s="442" t="s">
-        <v>1474</v>
-      </c>
-      <c r="C131" s="442"/>
-      <c r="D131" s="311" t="s">
-        <v>1503</v>
-      </c>
-      <c r="E131" s="511" t="s">
-        <v>1488</v>
-      </c>
-      <c r="F131" s="511"/>
-      <c r="G131" s="511"/>
-      <c r="H131" s="511"/>
-      <c r="I131" s="511"/>
-      <c r="J131" s="511"/>
-      <c r="K131" s="511"/>
+    <row r="131" spans="12:12" ht="54.000000">
       <c r="L131" s="463"/>
     </row>
-    <row r="132" spans="1:12" ht="54.000000">
-      <c r="A132" s="442" t="s">
-        <v>1587</v>
-      </c>
-      <c r="B132" s="463" t="s">
-        <v>1494</v>
-      </c>
-      <c r="C132" s="463"/>
-      <c r="D132" s="588" t="s">
-        <v>1512</v>
-      </c>
-      <c r="E132" s="511" t="s">
-        <v>1514</v>
-      </c>
-      <c r="F132" s="511"/>
-      <c r="G132" s="511"/>
-      <c r="H132" s="511"/>
-      <c r="I132" s="511"/>
-      <c r="J132" s="511"/>
-      <c r="K132" s="511"/>
+    <row r="132" spans="12:12" ht="42.750000">
       <c r="L132" s="463"/>
     </row>
-    <row r="133" spans="1:12" ht="42.750000">
-      <c r="A133" s="442" t="s">
-        <v>1508</v>
-      </c>
-      <c r="B133" s="463" t="s">
-        <v>1494</v>
-      </c>
-      <c r="C133" s="463"/>
-      <c r="D133" s="311" t="s">
-        <v>1511</v>
-      </c>
-      <c r="E133" s="551" t="s">
-        <v>1516</v>
-      </c>
-      <c r="F133" s="551"/>
-      <c r="G133" s="551"/>
-      <c r="H133" s="551"/>
-      <c r="I133" s="551"/>
-      <c r="J133" s="551"/>
-      <c r="K133" s="551"/>
+    <row r="133" spans="12:12" ht="42.750000">
       <c r="L133" s="463"/>
     </row>
-    <row r="134" spans="1:12" ht="42.750000">
-      <c r="A134" s="442" t="s">
-        <v>1517</v>
-      </c>
-      <c r="B134" s="442" t="s">
-        <v>1494</v>
-      </c>
-      <c r="C134" s="442"/>
-      <c r="D134" s="311" t="s">
-        <v>1592</v>
-      </c>
-      <c r="E134" s="551" t="s">
-        <v>1584</v>
-      </c>
-      <c r="F134" s="551"/>
-      <c r="G134" s="551"/>
-      <c r="H134" s="551"/>
-      <c r="I134" s="551"/>
-      <c r="J134" s="551"/>
-      <c r="K134" s="551"/>
+    <row r="134" spans="12:12" ht="57.000000">
       <c r="L134" s="463"/>
     </row>
-    <row r="135" spans="1:12" ht="57.000000">
-      <c r="A135" s="442" t="s">
-        <v>1520</v>
-      </c>
-      <c r="B135" s="442" t="s">
-        <v>1521</v>
-      </c>
-      <c r="C135" s="442"/>
-      <c r="D135" s="311" t="s">
-        <v>1593</v>
-      </c>
-      <c r="E135" s="551" t="s">
-        <v>1595</v>
-      </c>
-      <c r="F135" s="551"/>
-      <c r="G135" s="551"/>
-      <c r="H135" s="551"/>
-      <c r="I135" s="551"/>
-      <c r="J135" s="551"/>
-      <c r="K135" s="551"/>
+    <row r="135" spans="12:12" ht="57.000000">
       <c r="L135" s="463"/>
     </row>
-    <row r="136" spans="1:12" ht="57.000000">
-      <c r="A136" s="442" t="s">
-        <v>1596</v>
-      </c>
-      <c r="B136" s="442" t="s">
-        <v>1522</v>
-      </c>
-      <c r="C136" s="442"/>
-      <c r="D136" s="311" t="s">
-        <v>1597</v>
-      </c>
-      <c r="E136" s="551" t="s">
-        <v>1600</v>
-      </c>
-      <c r="F136" s="551"/>
-      <c r="G136" s="551"/>
-      <c r="H136" s="551"/>
-      <c r="I136" s="551"/>
-      <c r="J136" s="551"/>
-      <c r="K136" s="551"/>
+    <row r="136" spans="12:12" ht="42.750000">
       <c r="L136" s="463"/>
     </row>
-    <row r="137" spans="1:12" ht="42.750000">
-      <c r="A137" s="442" t="s">
-        <v>330</v>
-      </c>
-      <c r="B137" s="442" t="s">
-        <v>1523</v>
-      </c>
-      <c r="C137" s="442"/>
-      <c r="D137" s="311" t="s">
-        <v>1601</v>
-      </c>
-      <c r="E137" s="551" t="s">
-        <v>1605</v>
-      </c>
-      <c r="F137" s="551"/>
-      <c r="G137" s="551"/>
-      <c r="H137" s="551"/>
-      <c r="I137" s="551"/>
-      <c r="J137" s="551"/>
-      <c r="K137" s="551"/>
+    <row r="137" spans="12:12" ht="42.750000">
       <c r="L137" s="463"/>
     </row>
-    <row r="138" spans="1:12" ht="42.750000">
-      <c r="A138" s="442" t="s">
-        <v>1606</v>
-      </c>
-      <c r="B138" s="442" t="s">
-        <v>1524</v>
-      </c>
-      <c r="C138" s="442"/>
-      <c r="D138" s="311" t="s">
-        <v>1607</v>
-      </c>
-      <c r="E138" s="551" t="s">
-        <v>1608</v>
-      </c>
-      <c r="F138" s="551"/>
-      <c r="G138" s="551"/>
-      <c r="H138" s="551"/>
-      <c r="I138" s="551"/>
-      <c r="J138" s="551"/>
-      <c r="K138" s="551"/>
+    <row r="138" spans="12:12" ht="42.750000">
       <c r="L138" s="463"/>
     </row>
-    <row r="139" spans="1:12" ht="42.750000">
-      <c r="A139" s="442" t="s">
-        <v>1609</v>
-      </c>
-      <c r="B139" s="442" t="s">
-        <v>1525</v>
-      </c>
-      <c r="C139" s="442"/>
-      <c r="D139" s="311" t="s">
-        <v>1610</v>
-      </c>
-      <c r="E139" s="551" t="s">
-        <v>1611</v>
-      </c>
-      <c r="F139" s="551"/>
-      <c r="G139" s="551"/>
-      <c r="H139" s="551"/>
-      <c r="I139" s="551"/>
-      <c r="J139" s="551"/>
-      <c r="K139" s="551"/>
+    <row r="139" spans="12:12" ht="42.750000">
       <c r="L139" s="463"/>
     </row>
-    <row r="140" spans="1:12" ht="42.750000">
-      <c r="A140" s="442" t="s">
-        <v>1612</v>
-      </c>
-      <c r="B140" s="442" t="s">
-        <v>1526</v>
-      </c>
-      <c r="C140" s="442"/>
-      <c r="D140" s="311" t="s">
-        <v>1613</v>
-      </c>
-      <c r="E140" s="551" t="s">
-        <v>1615</v>
-      </c>
-      <c r="F140" s="551"/>
-      <c r="G140" s="551"/>
-      <c r="H140" s="551"/>
-      <c r="I140" s="551"/>
-      <c r="J140" s="551"/>
-      <c r="K140" s="551"/>
+    <row r="140" spans="12:12" ht="42.750000">
       <c r="L140" s="463"/>
     </row>
-    <row r="141" spans="1:12" ht="42.750000">
-      <c r="A141" s="442" t="s">
-        <v>1616</v>
-      </c>
-      <c r="B141" s="442" t="s">
-        <v>1527</v>
-      </c>
-      <c r="C141" s="442"/>
-      <c r="D141" s="311" t="s">
-        <v>1618</v>
-      </c>
-      <c r="E141" s="551" t="s">
-        <v>1619</v>
-      </c>
-      <c r="F141" s="551"/>
-      <c r="G141" s="551"/>
-      <c r="H141" s="551"/>
-      <c r="I141" s="551"/>
-      <c r="J141" s="551"/>
-      <c r="K141" s="551"/>
+    <row r="141" spans="12:12" ht="42.750000">
       <c r="L141" s="463"/>
     </row>
-    <row r="142" spans="1:12" ht="42.750000">
-      <c r="A142" s="442" t="s">
-        <v>1620</v>
-      </c>
-      <c r="B142" s="442" t="s">
-        <v>1528</v>
-      </c>
-      <c r="C142" s="442"/>
-      <c r="D142" s="311" t="s">
-        <v>1627</v>
-      </c>
-      <c r="E142" s="567"/>
-      <c r="F142" s="567"/>
-      <c r="G142" s="567"/>
-      <c r="H142" s="567"/>
-      <c r="I142" s="567"/>
-      <c r="J142" s="567"/>
-      <c r="K142" s="567"/>
+    <row r="142" spans="12:12" ht="28.500000">
       <c r="L142" s="463"/>
     </row>
-    <row r="143" spans="1:12" ht="28.500000">
-      <c r="A143" s="442" t="s">
-        <v>1622</v>
-      </c>
-      <c r="B143" s="442" t="s">
-        <v>1529</v>
-      </c>
-      <c r="C143" s="442"/>
-      <c r="D143" s="311" t="s">
-        <v>1628</v>
-      </c>
-      <c r="E143" s="551" t="s">
-        <v>1624</v>
-      </c>
-      <c r="F143" s="551"/>
-      <c r="G143" s="551"/>
-      <c r="H143" s="551"/>
-      <c r="I143" s="551"/>
-      <c r="J143" s="551"/>
-      <c r="K143" s="551"/>
+    <row r="143" spans="12:12" ht="42.750000">
       <c r="L143" s="463"/>
     </row>
-    <row r="144" spans="1:12" ht="42.750000">
-      <c r="A144" s="442" t="s">
-        <v>1625</v>
-      </c>
-      <c r="B144" s="442" t="s">
-        <v>1530</v>
-      </c>
-      <c r="C144" s="442"/>
-      <c r="D144" s="311" t="s">
-        <v>1630</v>
-      </c>
-      <c r="E144" s="551" t="s">
-        <v>1633</v>
-      </c>
-      <c r="F144" s="551"/>
-      <c r="G144" s="551"/>
-      <c r="H144" s="551"/>
-      <c r="I144" s="551"/>
-      <c r="J144" s="551"/>
-      <c r="K144" s="551"/>
+    <row r="144" spans="12:12" ht="42.750000">
       <c r="L144" s="463"/>
     </row>
     <row r="145" spans="1:12" ht="42.750000">
-      <c r="A145" s="442" t="s">
-        <v>1634</v>
-      </c>
-      <c r="B145" s="442" t="s">
-        <v>1531</v>
-      </c>
-      <c r="C145" s="442"/>
-      <c r="D145" s="311" t="s">
-        <v>1635</v>
-      </c>
-      <c r="E145" s="551" t="s">
-        <v>1636</v>
-      </c>
-      <c r="F145" s="551"/>
-      <c r="G145" s="551"/>
-      <c r="H145" s="551"/>
-      <c r="I145" s="551"/>
-      <c r="J145" s="551"/>
-      <c r="K145" s="551"/>
       <c r="L145" s="463"/>
     </row>
     <row r="146" spans="1:12" ht="42.750000">
-      <c r="A146" s="442" t="s">
-        <v>1637</v>
-      </c>
-      <c r="B146" s="442" t="s">
-        <v>1532</v>
-      </c>
-      <c r="C146" s="442"/>
-      <c r="D146" s="311" t="s">
-        <v>1638</v>
-      </c>
-      <c r="E146" s="551" t="s">
-        <v>1639</v>
-      </c>
-      <c r="F146" s="551"/>
-      <c r="G146" s="551"/>
-      <c r="H146" s="551"/>
-      <c r="I146" s="551"/>
-      <c r="J146" s="551"/>
-      <c r="K146" s="551"/>
       <c r="L146" s="463"/>
     </row>
-    <row r="147" spans="1:12" ht="42.750000">
-      <c r="A147" s="442" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B147" s="442" t="s">
-        <v>1533</v>
-      </c>
-      <c r="C147" s="442"/>
-      <c r="D147" s="311" t="s">
-        <v>1646</v>
-      </c>
-      <c r="E147" s="551" t="s">
-        <v>1642</v>
-      </c>
-      <c r="F147" s="551"/>
-      <c r="G147" s="551"/>
-      <c r="H147" s="551"/>
-      <c r="I147" s="551"/>
-      <c r="J147" s="551"/>
-      <c r="K147" s="551"/>
+    <row r="147" spans="1:12" ht="28.500000">
       <c r="L147" s="463"/>
     </row>
     <row r="148" spans="1:12" ht="28.500000">
-      <c r="A148" s="442" t="s">
-        <v>1643</v>
-      </c>
-      <c r="B148" s="442" t="s">
-        <v>1534</v>
-      </c>
-      <c r="C148" s="442"/>
-      <c r="D148" s="311" t="s">
-        <v>1644</v>
-      </c>
-      <c r="E148" s="551" t="s">
-        <v>1647</v>
-      </c>
-      <c r="F148" s="551"/>
-      <c r="G148" s="551"/>
-      <c r="H148" s="551"/>
-      <c r="I148" s="551"/>
-      <c r="J148" s="551"/>
-      <c r="K148" s="551"/>
       <c r="L148" s="463"/>
     </row>
-    <row r="149" spans="1:12" ht="28.500000">
+    <row r="149" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A149" s="464"/>
-      <c r="B149" s="442" t="s">
-        <v>1535</v>
-      </c>
+      <c r="B149" s="442"/>
       <c r="C149" s="442"/>
-      <c r="D149" s="311" t="s">
-        <v>1645</v>
-      </c>
-      <c r="E149" s="551" t="s">
-        <v>1648</v>
-      </c>
-      <c r="F149" s="551"/>
-      <c r="G149" s="551"/>
-      <c r="H149" s="551"/>
-      <c r="I149" s="551"/>
-      <c r="J149" s="551"/>
-      <c r="K149" s="551"/>
       <c r="L149" s="463"/>
     </row>
     <row r="150" spans="1:12" ht="17.250000" customHeight="1">
-      <c r="A150" s="464"/>
-      <c r="B150" s="442"/>
-      <c r="C150" s="442"/>
-      <c r="F150" s="463"/>
-      <c r="G150" s="463"/>
-      <c r="H150" s="463"/>
-      <c r="I150" s="463"/>
-      <c r="J150" s="463"/>
-      <c r="K150" s="463"/>
+      <c r="A150" s="463"/>
+      <c r="C150" s="463"/>
       <c r="L150" s="463"/>
     </row>
     <row r="151" spans="1:12" ht="17.250000" customHeight="1">
@@ -22050,7 +21693,7 @@
       <c r="K268" s="463"/>
       <c r="L268" s="463"/>
     </row>
-    <row r="269" spans="1:12" ht="17.250000" customHeight="1">
+    <row r="269" spans="1:12">
       <c r="A269" s="463"/>
       <c r="C269" s="463"/>
       <c r="F269" s="463"/>
@@ -22381,8 +22024,11 @@
       <c r="L298" s="463"/>
     </row>
     <row r="299" spans="1:12">
-      <c r="A299" s="463"/>
-      <c r="C299" s="463"/>
+      <c r="A299" s="80" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B299" s="80"/>
+      <c r="C299" s="80"/>
       <c r="F299" s="463"/>
       <c r="G299" s="463"/>
       <c r="H299" s="463"/>
@@ -22392,8 +22038,13 @@
       <c r="L299" s="463"/>
     </row>
     <row r="300" spans="1:12">
-      <c r="A300" s="463"/>
-      <c r="C300" s="463"/>
+      <c r="A300" s="80" t="s">
+        <v>19</v>
+      </c>
+      <c r="B300" s="435" t="s">
+        <v>178</v>
+      </c>
+      <c r="C300" s="435"/>
       <c r="F300" s="463"/>
       <c r="G300" s="463"/>
       <c r="H300" s="463"/>
@@ -22402,268 +22053,513 @@
       <c r="K300" s="463"/>
       <c r="L300" s="463"/>
     </row>
-    <row r="301" spans="1:12">
-      <c r="A301" s="463"/>
-      <c r="C301" s="463"/>
-      <c r="F301" s="463"/>
-      <c r="G301" s="463"/>
-      <c r="H301" s="463"/>
-      <c r="I301" s="463"/>
-      <c r="J301" s="463"/>
-      <c r="K301" s="463"/>
+    <row r="301" spans="1:12" ht="17.250000" customHeight="1">
+      <c r="A301" s="80" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B301" s="484" t="s">
+        <v>3</v>
+      </c>
+      <c r="C301" s="548"/>
+      <c r="D301" s="80"/>
+      <c r="E301" s="484"/>
+      <c r="F301" s="547"/>
+      <c r="G301" s="547"/>
+      <c r="H301" s="547"/>
+      <c r="I301" s="651"/>
+      <c r="J301" s="651"/>
+      <c r="K301" s="651"/>
       <c r="L301" s="463"/>
     </row>
-    <row r="302" spans="1:12" ht="17.250000" customHeight="1">
-      <c r="A302" s="463"/>
-      <c r="C302" s="463"/>
-      <c r="F302" s="463"/>
-      <c r="G302" s="463"/>
-      <c r="H302" s="463"/>
-      <c r="I302" s="463"/>
-      <c r="J302" s="463"/>
-      <c r="K302" s="463"/>
+    <row r="302" spans="1:12">
+      <c r="A302" s="543" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B302" s="441" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C302" s="441"/>
+      <c r="E302" s="80" t="s">
+        <v>1</v>
+      </c>
+      <c r="F302" s="654">
+        <v>45940</v>
+      </c>
+      <c r="G302" s="441"/>
+      <c r="H302" s="441"/>
+      <c r="I302" s="441"/>
+      <c r="J302" s="441"/>
+      <c r="K302" s="492"/>
       <c r="L302" s="463"/>
     </row>
     <row r="303" spans="1:12">
-      <c r="A303" s="463"/>
-      <c r="C303" s="463"/>
+      <c r="A303" s="442" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B303" s="442" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C303" s="442"/>
+      <c r="D303" s="80" t="s">
+        <v>5</v>
+      </c>
+      <c r="E303" s="466" t="s">
+        <v>1455</v>
+      </c>
       <c r="F303" s="463"/>
-      <c r="G303" s="463"/>
-      <c r="H303" s="463"/>
-      <c r="I303" s="463"/>
-      <c r="J303" s="463"/>
-      <c r="K303" s="463"/>
+      <c r="G303" s="467"/>
+      <c r="H303" s="467"/>
+      <c r="I303" s="467"/>
+      <c r="J303" s="467"/>
+      <c r="K303" s="467"/>
       <c r="L303" s="463"/>
     </row>
-    <row r="304" spans="1:12">
-      <c r="A304" s="463"/>
-      <c r="C304" s="463"/>
-      <c r="F304" s="463"/>
-      <c r="G304" s="463"/>
-      <c r="H304" s="463"/>
-      <c r="I304" s="463"/>
-      <c r="J304" s="463"/>
-      <c r="K304" s="463"/>
+    <row r="304" spans="1:12" ht="42.750000">
+      <c r="A304" s="442" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B304" s="442" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C304" s="442"/>
+      <c r="D304" s="543" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E304" s="584" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F304" s="584"/>
+      <c r="G304" s="584"/>
+      <c r="H304" s="584"/>
+      <c r="I304" s="584"/>
+      <c r="J304" s="584"/>
+      <c r="K304" s="584"/>
       <c r="L304" s="463"/>
     </row>
-    <row r="305" spans="1:12">
-      <c r="A305" s="463"/>
+    <row r="305" spans="1:12" ht="42.750000">
+      <c r="A305" s="442" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B305" s="463" t="s">
+        <v>1494</v>
+      </c>
       <c r="C305" s="463"/>
-      <c r="F305" s="463"/>
-      <c r="G305" s="463"/>
-      <c r="H305" s="463"/>
-      <c r="I305" s="463"/>
-      <c r="J305" s="463"/>
-      <c r="K305" s="463"/>
+      <c r="D305" s="511" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E305" s="511" t="s">
+        <v>1473</v>
+      </c>
+      <c r="F305" s="511"/>
+      <c r="G305" s="511"/>
+      <c r="H305" s="511"/>
+      <c r="I305" s="511"/>
+      <c r="J305" s="511"/>
+      <c r="K305" s="511"/>
       <c r="L305" s="463"/>
     </row>
-    <row r="306" spans="1:12">
-      <c r="A306" s="463"/>
+    <row r="306" spans="1:12" ht="42.750000">
+      <c r="A306" s="442" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B306" s="463" t="s">
+        <v>1494</v>
+      </c>
       <c r="C306" s="463"/>
-      <c r="F306" s="463"/>
-      <c r="G306" s="463"/>
-      <c r="H306" s="463"/>
-      <c r="I306" s="463"/>
-      <c r="J306" s="463"/>
-      <c r="K306" s="463"/>
+      <c r="D306" s="311" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E306" s="511" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F306" s="511"/>
+      <c r="G306" s="511"/>
+      <c r="H306" s="511"/>
+      <c r="I306" s="511"/>
+      <c r="J306" s="511"/>
+      <c r="K306" s="511"/>
       <c r="L306" s="463"/>
     </row>
-    <row r="307" spans="1:12">
-      <c r="A307" s="463"/>
-      <c r="C307" s="463"/>
-      <c r="F307" s="463"/>
-      <c r="G307" s="463"/>
-      <c r="H307" s="463"/>
-      <c r="I307" s="463"/>
-      <c r="J307" s="463"/>
-      <c r="K307" s="463"/>
+    <row r="307" spans="1:12" ht="54.000000">
+      <c r="A307" s="442" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B307" s="442" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C307" s="442"/>
+      <c r="D307" s="588" t="s">
+        <v>1512</v>
+      </c>
+      <c r="E307" s="511" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F307" s="511"/>
+      <c r="G307" s="511"/>
+      <c r="H307" s="511"/>
+      <c r="I307" s="511"/>
+      <c r="J307" s="511"/>
+      <c r="K307" s="511"/>
       <c r="L307" s="463"/>
     </row>
-    <row r="308" spans="1:12">
-      <c r="A308" s="463"/>
-      <c r="C308" s="463"/>
-      <c r="F308" s="463"/>
-      <c r="G308" s="463"/>
-      <c r="H308" s="463"/>
-      <c r="I308" s="463"/>
-      <c r="J308" s="463"/>
-      <c r="K308" s="463"/>
+    <row r="308" spans="1:12" ht="42.750000">
+      <c r="A308" s="442" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B308" s="442" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C308" s="442"/>
+      <c r="D308" s="311" t="s">
+        <v>1511</v>
+      </c>
+      <c r="E308" s="551" t="s">
+        <v>1516</v>
+      </c>
+      <c r="F308" s="551"/>
+      <c r="G308" s="551"/>
+      <c r="H308" s="551"/>
+      <c r="I308" s="551"/>
+      <c r="J308" s="551"/>
+      <c r="K308" s="551"/>
       <c r="L308" s="463"/>
     </row>
-    <row r="309" spans="1:12">
-      <c r="A309" s="463"/>
-      <c r="C309" s="463"/>
-      <c r="F309" s="463"/>
-      <c r="G309" s="463"/>
-      <c r="H309" s="463"/>
-      <c r="I309" s="463"/>
-      <c r="J309" s="463"/>
-      <c r="K309" s="463"/>
+    <row r="309" spans="1:12" ht="42.750000">
+      <c r="A309" s="442" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B309" s="442" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C309" s="442"/>
+      <c r="D309" s="311" t="s">
+        <v>1592</v>
+      </c>
+      <c r="E309" s="551" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F309" s="551"/>
+      <c r="G309" s="551"/>
+      <c r="H309" s="551"/>
+      <c r="I309" s="551"/>
+      <c r="J309" s="551"/>
+      <c r="K309" s="551"/>
       <c r="L309" s="463"/>
     </row>
-    <row r="310" spans="1:12">
-      <c r="A310" s="463"/>
-      <c r="C310" s="463"/>
-      <c r="F310" s="463"/>
-      <c r="G310" s="463"/>
-      <c r="H310" s="463"/>
-      <c r="I310" s="463"/>
-      <c r="J310" s="463"/>
-      <c r="K310" s="463"/>
+    <row r="310" spans="1:12" ht="57.000000">
+      <c r="A310" s="442" t="s">
+        <v>330</v>
+      </c>
+      <c r="B310" s="442" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C310" s="442"/>
+      <c r="D310" s="311" t="s">
+        <v>1593</v>
+      </c>
+      <c r="E310" s="551" t="s">
+        <v>1595</v>
+      </c>
+      <c r="F310" s="551"/>
+      <c r="G310" s="551"/>
+      <c r="H310" s="551"/>
+      <c r="I310" s="551"/>
+      <c r="J310" s="551"/>
+      <c r="K310" s="551"/>
       <c r="L310" s="463"/>
     </row>
-    <row r="311" spans="1:12">
-      <c r="A311" s="463"/>
-      <c r="C311" s="463"/>
-      <c r="F311" s="463"/>
-      <c r="G311" s="463"/>
-      <c r="H311" s="463"/>
-      <c r="I311" s="463"/>
-      <c r="J311" s="463"/>
-      <c r="K311" s="463"/>
+    <row r="311" spans="1:12" ht="57.000000">
+      <c r="A311" s="442" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B311" s="442" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C311" s="442"/>
+      <c r="D311" s="311" t="s">
+        <v>1597</v>
+      </c>
+      <c r="E311" s="551" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F311" s="551"/>
+      <c r="G311" s="551"/>
+      <c r="H311" s="551"/>
+      <c r="I311" s="551"/>
+      <c r="J311" s="551"/>
+      <c r="K311" s="551"/>
       <c r="L311" s="463"/>
     </row>
-    <row r="312" spans="1:12">
-      <c r="A312" s="463"/>
-      <c r="C312" s="463"/>
-      <c r="F312" s="463"/>
-      <c r="G312" s="463"/>
-      <c r="H312" s="463"/>
-      <c r="I312" s="463"/>
-      <c r="J312" s="463"/>
-      <c r="K312" s="463"/>
+    <row r="312" spans="1:12" ht="42.750000">
+      <c r="A312" s="442" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B312" s="442" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C312" s="442"/>
+      <c r="D312" s="311" t="s">
+        <v>1601</v>
+      </c>
+      <c r="E312" s="551" t="s">
+        <v>1605</v>
+      </c>
+      <c r="F312" s="551"/>
+      <c r="G312" s="551"/>
+      <c r="H312" s="551"/>
+      <c r="I312" s="551"/>
+      <c r="J312" s="551"/>
+      <c r="K312" s="551"/>
       <c r="L312" s="463"/>
     </row>
-    <row r="313" spans="1:12">
-      <c r="A313" s="463"/>
-      <c r="C313" s="463"/>
-      <c r="F313" s="463"/>
-      <c r="G313" s="463"/>
-      <c r="H313" s="463"/>
-      <c r="I313" s="463"/>
-      <c r="J313" s="463"/>
-      <c r="K313" s="463"/>
+    <row r="313" spans="1:12" ht="42.750000">
+      <c r="A313" s="442" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B313" s="442" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C313" s="442"/>
+      <c r="D313" s="311" t="s">
+        <v>1607</v>
+      </c>
+      <c r="E313" s="551" t="s">
+        <v>1608</v>
+      </c>
+      <c r="F313" s="551"/>
+      <c r="G313" s="551"/>
+      <c r="H313" s="551"/>
+      <c r="I313" s="551"/>
+      <c r="J313" s="551"/>
+      <c r="K313" s="551"/>
       <c r="L313" s="463"/>
     </row>
-    <row r="314" spans="1:12">
-      <c r="A314" s="463"/>
-      <c r="C314" s="463"/>
-      <c r="F314" s="463"/>
-      <c r="G314" s="463"/>
-      <c r="H314" s="463"/>
-      <c r="I314" s="463"/>
-      <c r="J314" s="463"/>
-      <c r="K314" s="463"/>
+    <row r="314" spans="1:12" ht="42.750000">
+      <c r="A314" s="442" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B314" s="442" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C314" s="442"/>
+      <c r="D314" s="311" t="s">
+        <v>1610</v>
+      </c>
+      <c r="E314" s="551" t="s">
+        <v>1611</v>
+      </c>
+      <c r="F314" s="551"/>
+      <c r="G314" s="551"/>
+      <c r="H314" s="551"/>
+      <c r="I314" s="551"/>
+      <c r="J314" s="551"/>
+      <c r="K314" s="551"/>
       <c r="L314" s="463"/>
     </row>
-    <row r="315" spans="1:12">
-      <c r="A315" s="463"/>
-      <c r="C315" s="463"/>
-      <c r="F315" s="463"/>
-      <c r="G315" s="463"/>
-      <c r="H315" s="463"/>
-      <c r="I315" s="463"/>
-      <c r="J315" s="463"/>
-      <c r="K315" s="463"/>
+    <row r="315" spans="1:12" ht="42.750000">
+      <c r="A315" s="442" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B315" s="442" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C315" s="442"/>
+      <c r="D315" s="311" t="s">
+        <v>1613</v>
+      </c>
+      <c r="E315" s="551" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F315" s="551"/>
+      <c r="G315" s="551"/>
+      <c r="H315" s="551"/>
+      <c r="I315" s="551"/>
+      <c r="J315" s="551"/>
+      <c r="K315" s="551"/>
       <c r="L315" s="463"/>
     </row>
-    <row r="316" spans="1:12">
-      <c r="A316" s="463"/>
-      <c r="C316" s="463"/>
-      <c r="F316" s="463"/>
-      <c r="G316" s="463"/>
-      <c r="H316" s="463"/>
-      <c r="I316" s="463"/>
-      <c r="J316" s="463"/>
-      <c r="K316" s="463"/>
+    <row r="316" spans="1:12" ht="17.250000" customHeight="1">
+      <c r="A316" s="442" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B316" s="442" t="s">
+        <v>1529</v>
+      </c>
+      <c r="C316" s="442"/>
+      <c r="D316" s="311" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E316" s="551" t="s">
+        <v>1619</v>
+      </c>
+      <c r="F316" s="551"/>
+      <c r="G316" s="551"/>
+      <c r="H316" s="551"/>
+      <c r="I316" s="551"/>
+      <c r="J316" s="551"/>
+      <c r="K316" s="551"/>
       <c r="L316" s="463"/>
     </row>
     <row r="317" spans="1:12" ht="17.250000" customHeight="1">
-      <c r="A317" s="463"/>
-      <c r="C317" s="463"/>
-      <c r="F317" s="463"/>
-      <c r="G317" s="463"/>
-      <c r="H317" s="463"/>
-      <c r="I317" s="463"/>
-      <c r="J317" s="463"/>
-      <c r="K317" s="463"/>
+      <c r="A317" s="442" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B317" s="442" t="s">
+        <v>1530</v>
+      </c>
+      <c r="C317" s="442"/>
+      <c r="D317" s="311" t="s">
+        <v>1627</v>
+      </c>
+      <c r="E317" s="567"/>
+      <c r="F317" s="567"/>
+      <c r="G317" s="567"/>
+      <c r="H317" s="567"/>
+      <c r="I317" s="567"/>
+      <c r="J317" s="567"/>
+      <c r="K317" s="567"/>
       <c r="L317" s="463"/>
     </row>
     <row r="318" spans="1:12" ht="17.250000" customHeight="1">
-      <c r="A318" s="463"/>
-      <c r="C318" s="463"/>
-      <c r="F318" s="463"/>
-      <c r="G318" s="463"/>
-      <c r="H318" s="463"/>
-      <c r="I318" s="463"/>
-      <c r="J318" s="463"/>
-      <c r="K318" s="463"/>
+      <c r="A318" s="442" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B318" s="442" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C318" s="442"/>
+      <c r="D318" s="311" t="s">
+        <v>1628</v>
+      </c>
+      <c r="E318" s="551" t="s">
+        <v>1624</v>
+      </c>
+      <c r="F318" s="551"/>
+      <c r="G318" s="551"/>
+      <c r="H318" s="551"/>
+      <c r="I318" s="551"/>
+      <c r="J318" s="551"/>
+      <c r="K318" s="551"/>
       <c r="L318" s="463"/>
     </row>
     <row r="319" spans="1:12" ht="17.250000" customHeight="1">
-      <c r="A319" s="463"/>
-      <c r="C319" s="463"/>
-      <c r="F319" s="463"/>
-      <c r="G319" s="463"/>
-      <c r="H319" s="463"/>
-      <c r="I319" s="463"/>
-      <c r="J319" s="463"/>
-      <c r="K319" s="463"/>
+      <c r="A319" s="442" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B319" s="442" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C319" s="442"/>
+      <c r="D319" s="311" t="s">
+        <v>1630</v>
+      </c>
+      <c r="E319" s="551" t="s">
+        <v>1633</v>
+      </c>
+      <c r="F319" s="551"/>
+      <c r="G319" s="551"/>
+      <c r="H319" s="551"/>
+      <c r="I319" s="551"/>
+      <c r="J319" s="551"/>
+      <c r="K319" s="551"/>
       <c r="L319" s="463"/>
     </row>
     <row r="320" spans="1:12" ht="17.250000" customHeight="1">
-      <c r="A320" s="463"/>
-      <c r="C320" s="463"/>
-      <c r="F320" s="463"/>
-      <c r="G320" s="463"/>
-      <c r="H320" s="463"/>
-      <c r="I320" s="463"/>
-      <c r="J320" s="463"/>
-      <c r="K320" s="463"/>
+      <c r="A320" s="442" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B320" s="442" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C320" s="442"/>
+      <c r="D320" s="311" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E320" s="551" t="s">
+        <v>1636</v>
+      </c>
+      <c r="F320" s="551"/>
+      <c r="G320" s="551"/>
+      <c r="H320" s="551"/>
+      <c r="I320" s="551"/>
+      <c r="J320" s="551"/>
+      <c r="K320" s="551"/>
       <c r="L320" s="463"/>
     </row>
     <row r="321" spans="1:12" ht="17.250000" customHeight="1">
-      <c r="A321" s="463"/>
-      <c r="C321" s="463"/>
-      <c r="F321" s="463"/>
-      <c r="G321" s="463"/>
-      <c r="H321" s="463"/>
-      <c r="I321" s="463"/>
-      <c r="J321" s="463"/>
-      <c r="K321" s="463"/>
+      <c r="A321" s="442" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B321" s="442" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C321" s="442"/>
+      <c r="D321" s="311" t="s">
+        <v>1638</v>
+      </c>
+      <c r="E321" s="551" t="s">
+        <v>1639</v>
+      </c>
+      <c r="F321" s="551"/>
+      <c r="G321" s="551"/>
+      <c r="H321" s="551"/>
+      <c r="I321" s="551"/>
+      <c r="J321" s="551"/>
+      <c r="K321" s="551"/>
       <c r="L321" s="463"/>
     </row>
     <row r="322" spans="1:12" ht="17.250000" customHeight="1">
-      <c r="A322" s="463"/>
-      <c r="C322" s="463"/>
-      <c r="F322" s="463"/>
-      <c r="G322" s="463"/>
-      <c r="H322" s="463"/>
-      <c r="I322" s="463"/>
-      <c r="J322" s="463"/>
-      <c r="K322" s="463"/>
+      <c r="A322" s="464"/>
+      <c r="B322" s="442" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C322" s="442"/>
+      <c r="D322" s="311" t="s">
+        <v>1646</v>
+      </c>
+      <c r="E322" s="551" t="s">
+        <v>1642</v>
+      </c>
+      <c r="F322" s="551"/>
+      <c r="G322" s="551"/>
+      <c r="H322" s="551"/>
+      <c r="I322" s="551"/>
+      <c r="J322" s="551"/>
+      <c r="K322" s="551"/>
       <c r="L322" s="463"/>
     </row>
     <row r="323" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A323" s="463"/>
       <c r="C323" s="463"/>
-      <c r="F323" s="463"/>
-      <c r="G323" s="463"/>
-      <c r="H323" s="463"/>
-      <c r="I323" s="463"/>
-      <c r="J323" s="463"/>
-      <c r="K323" s="463"/>
+      <c r="D323" s="311" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E323" s="551" t="s">
+        <v>1647</v>
+      </c>
+      <c r="F323" s="551"/>
+      <c r="G323" s="551"/>
+      <c r="H323" s="551"/>
+      <c r="I323" s="551"/>
+      <c r="J323" s="551"/>
+      <c r="K323" s="551"/>
       <c r="L323" s="463"/>
     </row>
     <row r="324" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A324" s="463"/>
       <c r="C324" s="463"/>
-      <c r="F324" s="463"/>
-      <c r="G324" s="463"/>
-      <c r="H324" s="463"/>
-      <c r="I324" s="463"/>
-      <c r="J324" s="463"/>
-      <c r="K324" s="463"/>
+      <c r="D324" s="311" t="s">
+        <v>1645</v>
+      </c>
+      <c r="E324" s="551" t="s">
+        <v>1648</v>
+      </c>
+      <c r="F324" s="551"/>
+      <c r="G324" s="551"/>
+      <c r="H324" s="551"/>
+      <c r="I324" s="551"/>
+      <c r="J324" s="551"/>
+      <c r="K324" s="551"/>
       <c r="L324" s="463"/>
     </row>
     <row r="325" spans="1:12" ht="17.250000" customHeight="1">
@@ -22974,7 +22870,7 @@
       <c r="K352" s="463"/>
       <c r="L352" s="463"/>
     </row>
-    <row r="353" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="353" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A353" s="463"/>
       <c r="C353" s="463"/>
       <c r="F353" s="463"/>
@@ -22985,7 +22881,7 @@
       <c r="K353" s="463"/>
       <c r="L353" s="463"/>
     </row>
-    <row r="354" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="354" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A354" s="463"/>
       <c r="C354" s="463"/>
       <c r="F354" s="463"/>
@@ -22996,7 +22892,7 @@
       <c r="K354" s="463"/>
       <c r="L354" s="463"/>
     </row>
-    <row r="355" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="355" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A355" s="463"/>
       <c r="C355" s="463"/>
       <c r="F355" s="463"/>
@@ -23007,7 +22903,7 @@
       <c r="K355" s="463"/>
       <c r="L355" s="463"/>
     </row>
-    <row r="356" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="356" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A356" s="463"/>
       <c r="C356" s="463"/>
       <c r="F356" s="463"/>
@@ -23018,7 +22914,7 @@
       <c r="K356" s="463"/>
       <c r="L356" s="463"/>
     </row>
-    <row r="357" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="357" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A357" s="463"/>
       <c r="C357" s="463"/>
       <c r="F357" s="463"/>
@@ -23029,7 +22925,7 @@
       <c r="K357" s="463"/>
       <c r="L357" s="463"/>
     </row>
-    <row r="358" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="358" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A358" s="463"/>
       <c r="C358" s="463"/>
       <c r="F358" s="463"/>
@@ -23040,7 +22936,7 @@
       <c r="K358" s="463"/>
       <c r="L358" s="463"/>
     </row>
-    <row r="359" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="359" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A359" s="463"/>
       <c r="C359" s="463"/>
       <c r="F359" s="463"/>
@@ -23051,7 +22947,7 @@
       <c r="K359" s="463"/>
       <c r="L359" s="463"/>
     </row>
-    <row r="360" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="360" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A360" s="463"/>
       <c r="C360" s="463"/>
       <c r="F360" s="463"/>
@@ -23062,7 +22958,7 @@
       <c r="K360" s="463"/>
       <c r="L360" s="463"/>
     </row>
-    <row r="361" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="361" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A361" s="463"/>
       <c r="C361" s="463"/>
       <c r="F361" s="463"/>
@@ -23073,7 +22969,7 @@
       <c r="K361" s="463"/>
       <c r="L361" s="463"/>
     </row>
-    <row r="362" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="362" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A362" s="463"/>
       <c r="C362" s="463"/>
       <c r="F362" s="463"/>
@@ -23084,7 +22980,7 @@
       <c r="K362" s="463"/>
       <c r="L362" s="463"/>
     </row>
-    <row r="363" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="363" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A363" s="463"/>
       <c r="C363" s="463"/>
       <c r="F363" s="463"/>
@@ -23095,7 +22991,7 @@
       <c r="K363" s="463"/>
       <c r="L363" s="463"/>
     </row>
-    <row r="364" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="364" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A364" s="463"/>
       <c r="C364" s="463"/>
       <c r="F364" s="463"/>
@@ -23106,130 +23002,109 @@
       <c r="K364" s="463"/>
       <c r="L364" s="463"/>
     </row>
-    <row r="365" spans="1:13" ht="17.250000" customHeight="1">
-      <c r="A365" s="463"/>
-      <c r="C365" s="463"/>
-      <c r="D365" s="311"/>
+    <row r="365" spans="1:12" ht="17.250000" customHeight="1">
+      <c r="F365" s="463"/>
+      <c r="G365" s="463"/>
+      <c r="H365" s="463"/>
+      <c r="I365" s="463"/>
+      <c r="J365" s="463"/>
+      <c r="K365" s="463"/>
       <c r="L365" s="463"/>
     </row>
-    <row r="366" spans="1:13" ht="17.250000" customHeight="1">
-      <c r="D366" s="311"/>
+    <row r="366" spans="1:12" ht="17.250000" customHeight="1">
       <c r="L366" s="463"/>
     </row>
-    <row r="367" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="367" spans="1:12" ht="17.250000" customHeight="1">
       <c r="L367" s="463"/>
-      <c r="M367" s="460"/>
-    </row>
-    <row r="368" spans="1:13" ht="17.250000" customHeight="1">
-      <c r="L368" s="463"/>
-      <c r="M368" s="460"/>
-    </row>
-    <row r="369" spans="2:13" ht="17.250000" customHeight="1">
-      <c r="L369" s="507"/>
-      <c r="M369" s="460"/>
-    </row>
-    <row r="370" spans="2:13" ht="17.250000" customHeight="1">
+    </row>
+    <row r="368" spans="1:12" ht="17.250000" customHeight="1">
+      <c r="L368" s="507"/>
+    </row>
+    <row r="369" spans="2:12" ht="17.250000" customHeight="1">
+      <c r="B369" s="311"/>
+      <c r="L369" s="464"/>
+    </row>
+    <row r="370" spans="2:12">
       <c r="B370" s="311"/>
-      <c r="C370" s="311"/>
-      <c r="L370" s="464"/>
-    </row>
-    <row r="371" spans="2:13">
-      <c r="B371" s="311"/>
-      <c r="C371" s="311"/>
-    </row>
-    <row r="373" spans="2:13">
+    </row>
+    <row r="372" spans="2:12">
+      <c r="L372" s="511"/>
+    </row>
+    <row r="373" spans="2:12" ht="54.000000" customHeight="1">
+      <c r="B373" s="311"/>
       <c r="L373" s="511"/>
     </row>
-    <row r="374" spans="2:13" ht="54.000000" customHeight="1">
+    <row r="374" spans="2:12" ht="42.750000" customHeight="1">
       <c r="B374" s="311"/>
-      <c r="C374" s="311"/>
-      <c r="L374" s="511"/>
-    </row>
-    <row r="375" spans="2:13" ht="42.750000" customHeight="1">
-      <c r="B375" s="311"/>
-      <c r="C375" s="311"/>
+      <c r="L374" s="551"/>
+    </row>
+    <row r="375" spans="2:12" ht="42.750000">
       <c r="L375" s="551"/>
     </row>
-    <row r="376" spans="2:13" ht="42.750000">
+    <row r="376" spans="2:12" ht="57.000000">
+      <c r="B376" s="311"/>
       <c r="L376" s="551"/>
     </row>
-    <row r="377" spans="2:13" ht="57.000000">
+    <row r="377" spans="2:12" ht="57.000000">
       <c r="B377" s="311"/>
-      <c r="C377" s="311"/>
       <c r="L377" s="551"/>
     </row>
-    <row r="378" spans="2:13" ht="57.000000">
+    <row r="378" spans="2:12" ht="42.750000">
       <c r="B378" s="311"/>
-      <c r="C378" s="311"/>
       <c r="L378" s="551"/>
     </row>
-    <row r="379" spans="2:13" ht="42.750000">
+    <row r="379" spans="2:12" ht="42.750000">
       <c r="B379" s="311"/>
-      <c r="C379" s="311"/>
       <c r="L379" s="551"/>
     </row>
-    <row r="380" spans="2:13" ht="42.750000">
+    <row r="380" spans="2:12" ht="42.750000">
       <c r="B380" s="311"/>
-      <c r="C380" s="311"/>
       <c r="L380" s="551"/>
     </row>
-    <row r="381" spans="2:13" ht="42.750000">
-      <c r="B381" s="311"/>
-      <c r="C381" s="311"/>
+    <row r="381" spans="2:12" ht="42.750000">
       <c r="L381" s="551"/>
     </row>
-    <row r="382" spans="2:13" ht="42.750000">
+    <row r="382" spans="2:12" ht="42.750000">
+      <c r="B382" s="311"/>
       <c r="L382" s="551"/>
     </row>
-    <row r="383" spans="2:13" ht="42.750000">
-      <c r="B383" s="311"/>
-      <c r="C383" s="311"/>
+    <row r="383" spans="2:12" ht="42.750000">
       <c r="L383" s="551"/>
     </row>
-    <row r="384" spans="2:13" ht="42.750000">
+    <row r="384" spans="2:12" ht="28.500000">
+      <c r="B384" s="311"/>
       <c r="L384" s="551"/>
     </row>
-    <row r="385" spans="1:12" ht="28.500000">
+    <row r="385" spans="1:12" ht="42.750000">
       <c r="B385" s="311"/>
-      <c r="C385" s="311"/>
       <c r="L385" s="551"/>
     </row>
     <row r="386" spans="1:12" ht="42.750000">
       <c r="B386" s="311"/>
-      <c r="C386" s="311"/>
       <c r="L386" s="551"/>
     </row>
     <row r="387" spans="1:12" ht="42.750000">
       <c r="B387" s="311"/>
-      <c r="C387" s="311"/>
       <c r="L387" s="551"/>
     </row>
     <row r="388" spans="1:12" ht="42.750000">
       <c r="B388" s="311"/>
-      <c r="C388" s="311"/>
       <c r="L388" s="551"/>
     </row>
-    <row r="389" spans="1:12" ht="42.750000">
-      <c r="B389" s="311"/>
-      <c r="C389" s="311"/>
+    <row r="389" spans="1:12">
       <c r="L389" s="551"/>
     </row>
     <row r="390" spans="1:12">
+      <c r="B390" s="311"/>
       <c r="L390" s="551"/>
     </row>
-    <row r="391" spans="1:12">
-      <c r="B391" s="311"/>
-      <c r="C391" s="311"/>
+    <row r="391" spans="1:12" ht="17.250000" customHeight="1">
       <c r="L391" s="551"/>
     </row>
     <row r="392" spans="1:12" ht="17.250000" customHeight="1">
-      <c r="E392" s="567"/>
-      <c r="F392" s="567"/>
-      <c r="G392" s="567"/>
-      <c r="H392" s="567"/>
-      <c r="I392" s="567"/>
-      <c r="J392" s="567"/>
-      <c r="K392" s="567"/>
+      <c r="A392" s="464"/>
+      <c r="B392" s="442"/>
+      <c r="C392" s="442"/>
       <c r="L392" s="551"/>
     </row>
     <row r="393" spans="1:12" ht="17.250000" customHeight="1">
@@ -23678,7 +23553,6 @@
       <c r="A427" s="464"/>
       <c r="B427" s="442"/>
       <c r="C427" s="442"/>
-      <c r="D427" s="161"/>
       <c r="E427" s="567"/>
       <c r="F427" s="567"/>
       <c r="G427" s="567"/>
@@ -23693,13 +23567,13 @@
       <c r="B428" s="442"/>
       <c r="C428" s="442"/>
       <c r="D428" s="161"/>
-      <c r="E428" s="551"/>
-      <c r="F428" s="551"/>
-      <c r="G428" s="551"/>
-      <c r="H428" s="551"/>
-      <c r="I428" s="551"/>
-      <c r="J428" s="551"/>
-      <c r="K428" s="551"/>
+      <c r="E428" s="567"/>
+      <c r="F428" s="567"/>
+      <c r="G428" s="567"/>
+      <c r="H428" s="567"/>
+      <c r="I428" s="567"/>
+      <c r="J428" s="567"/>
+      <c r="K428" s="567"/>
       <c r="L428" s="551"/>
     </row>
     <row r="429" spans="1:12" ht="17.250000" customHeight="1">
@@ -23772,7 +23646,7 @@
       <c r="K433" s="551"/>
       <c r="L433" s="551"/>
     </row>
-    <row r="434" spans="1:12" ht="17.250000" customHeight="1">
+    <row r="434" spans="1:12">
       <c r="A434" s="464"/>
       <c r="B434" s="442"/>
       <c r="C434" s="442"/>
@@ -23802,8 +23676,8 @@
     </row>
     <row r="436" spans="1:12">
       <c r="A436" s="464"/>
-      <c r="B436" s="442"/>
-      <c r="C436" s="442"/>
+      <c r="B436" s="464"/>
+      <c r="C436" s="464"/>
       <c r="D436" s="161"/>
       <c r="E436" s="551"/>
       <c r="F436" s="551"/>
@@ -23832,6 +23706,7 @@
       <c r="A438" s="464"/>
       <c r="B438" s="464"/>
       <c r="C438" s="464"/>
+      <c r="D438" s="161"/>
       <c r="E438" s="551"/>
       <c r="F438" s="551"/>
       <c r="G438" s="551"/>
@@ -23845,7 +23720,6 @@
       <c r="A439" s="464"/>
       <c r="B439" s="464"/>
       <c r="C439" s="464"/>
-      <c r="D439" s="161"/>
       <c r="E439" s="551"/>
       <c r="F439" s="551"/>
       <c r="G439" s="551"/>
@@ -23859,6 +23733,7 @@
       <c r="A440" s="464"/>
       <c r="B440" s="464"/>
       <c r="C440" s="464"/>
+      <c r="D440" s="161"/>
       <c r="E440" s="551"/>
       <c r="F440" s="551"/>
       <c r="G440" s="551"/>
@@ -23885,7 +23760,6 @@
       <c r="A442" s="464"/>
       <c r="B442" s="464"/>
       <c r="C442" s="464"/>
-      <c r="D442" s="161"/>
       <c r="E442" s="551"/>
       <c r="F442" s="551"/>
       <c r="G442" s="551"/>
@@ -23899,6 +23773,7 @@
       <c r="A443" s="464"/>
       <c r="B443" s="464"/>
       <c r="C443" s="464"/>
+      <c r="D443" s="161"/>
       <c r="E443" s="551"/>
       <c r="F443" s="551"/>
       <c r="G443" s="551"/>
@@ -24010,25 +23885,26 @@
       <c r="I451" s="551"/>
       <c r="J451" s="551"/>
       <c r="K451" s="551"/>
-      <c r="L451" s="551"/>
+      <c r="L451" s="463"/>
     </row>
     <row r="452" spans="1:12">
       <c r="A452" s="464"/>
       <c r="B452" s="464"/>
       <c r="C452" s="464"/>
-      <c r="E452" s="463"/>
-      <c r="F452" s="463"/>
-      <c r="G452" s="463"/>
-      <c r="H452" s="463"/>
-      <c r="I452" s="463"/>
-      <c r="J452" s="463"/>
-      <c r="K452" s="463"/>
+      <c r="E452" s="551"/>
+      <c r="F452" s="551"/>
+      <c r="G452" s="551"/>
+      <c r="H452" s="551"/>
+      <c r="I452" s="551"/>
+      <c r="J452" s="551"/>
+      <c r="K452" s="551"/>
       <c r="L452" s="463"/>
     </row>
     <row r="453" spans="1:12">
       <c r="A453" s="464"/>
       <c r="B453" s="464"/>
       <c r="C453" s="464"/>
+      <c r="E453" s="463"/>
       <c r="F453" s="463"/>
       <c r="G453" s="463"/>
       <c r="H453" s="463"/>
@@ -24377,7 +24253,6 @@
       <c r="A482" s="464"/>
       <c r="B482" s="464"/>
       <c r="C482" s="464"/>
-      <c r="D482" s="161"/>
       <c r="F482" s="463"/>
       <c r="G482" s="463"/>
       <c r="H482" s="463"/>
@@ -24520,6 +24395,7 @@
       <c r="A493" s="464"/>
       <c r="B493" s="464"/>
       <c r="C493" s="464"/>
+      <c r="D493" s="161"/>
       <c r="F493" s="463"/>
       <c r="G493" s="463"/>
       <c r="H493" s="463"/>
@@ -24532,7 +24408,6 @@
       <c r="A494" s="464"/>
       <c r="B494" s="464"/>
       <c r="C494" s="464"/>
-      <c r="D494" s="161"/>
       <c r="F494" s="463"/>
       <c r="G494" s="463"/>
       <c r="H494" s="463"/>
@@ -24545,6 +24420,7 @@
       <c r="A495" s="464"/>
       <c r="B495" s="464"/>
       <c r="C495" s="464"/>
+      <c r="D495" s="161"/>
       <c r="F495" s="463"/>
       <c r="G495" s="463"/>
       <c r="H495" s="463"/>
@@ -24569,7 +24445,6 @@
       <c r="A497" s="464"/>
       <c r="B497" s="464"/>
       <c r="C497" s="464"/>
-      <c r="D497" s="161"/>
       <c r="F497" s="463"/>
       <c r="G497" s="463"/>
       <c r="H497" s="463"/>
@@ -24582,7 +24457,7 @@
       <c r="A498" s="464"/>
       <c r="B498" s="464"/>
       <c r="C498" s="464"/>
-      <c r="D498" s="311"/>
+      <c r="D498" s="161"/>
       <c r="F498" s="463"/>
       <c r="G498" s="463"/>
       <c r="H498" s="463"/>
@@ -24595,6 +24470,7 @@
       <c r="A499" s="464"/>
       <c r="B499" s="464"/>
       <c r="C499" s="464"/>
+      <c r="D499" s="311"/>
       <c r="F499" s="463"/>
       <c r="G499" s="463"/>
       <c r="H499" s="463"/>
@@ -24736,204 +24612,209 @@
       <c r="L510" s="463"/>
     </row>
     <row r="511" spans="1:12">
-      <c r="A511" s="464"/>
-      <c r="B511" s="464"/>
-      <c r="C511" s="464"/>
+      <c r="A511" s="311"/>
+      <c r="B511" s="463"/>
+      <c r="C511" s="311"/>
       <c r="F511" s="463"/>
       <c r="G511" s="463"/>
       <c r="H511" s="463"/>
       <c r="I511" s="463"/>
       <c r="J511" s="463"/>
       <c r="K511" s="463"/>
-      <c r="L511" s="463"/>
+      <c r="L511" s="311"/>
     </row>
     <row r="512" spans="1:12">
-      <c r="A512" s="311"/>
-      <c r="B512" s="463"/>
-      <c r="C512" s="311"/>
-      <c r="F512" s="311"/>
-      <c r="G512" s="311"/>
-      <c r="H512" s="311"/>
-      <c r="I512" s="311"/>
-      <c r="J512" s="311"/>
-      <c r="K512" s="311"/>
-      <c r="L512" s="311"/>
+      <c r="F512" s="463"/>
+      <c r="G512" s="463"/>
+      <c r="H512" s="463"/>
+      <c r="I512" s="463"/>
+      <c r="J512" s="463"/>
+      <c r="K512" s="463"/>
+    </row>
+    <row r="513">
+      <c r="F513" s="311"/>
+      <c r="G513" s="311"/>
+      <c r="H513" s="311"/>
+      <c r="I513" s="311"/>
+      <c r="J513" s="311"/>
+      <c r="K513" s="311"/>
     </row>
   </sheetData>
   <mergeCells count="182">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="F2:L2"/>
-    <mergeCell ref="A4:A56"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="L4:L7"/>
-    <mergeCell ref="B8:B13"/>
-    <mergeCell ref="C8:C13"/>
-    <mergeCell ref="L8:L13"/>
-    <mergeCell ref="B14:B22"/>
-    <mergeCell ref="C14:C22"/>
-    <mergeCell ref="L14:L22"/>
-    <mergeCell ref="B24:B36"/>
-    <mergeCell ref="C24:C36"/>
-    <mergeCell ref="L24:L36"/>
-    <mergeCell ref="B37:B40"/>
-    <mergeCell ref="C37:C40"/>
-    <mergeCell ref="L37:L39"/>
-    <mergeCell ref="L40:L52"/>
-    <mergeCell ref="B41:B52"/>
-    <mergeCell ref="C41:C52"/>
-    <mergeCell ref="B53:B56"/>
-    <mergeCell ref="C53:C56"/>
-    <mergeCell ref="L53:L56"/>
-    <mergeCell ref="A57:A78"/>
-    <mergeCell ref="B57:B66"/>
-    <mergeCell ref="C57:C66"/>
-    <mergeCell ref="D59:D66"/>
-    <mergeCell ref="E59:E66"/>
-    <mergeCell ref="F59:F66"/>
-    <mergeCell ref="G59:G66"/>
-    <mergeCell ref="H59:H66"/>
-    <mergeCell ref="I59:I66"/>
-    <mergeCell ref="J59:J66"/>
-    <mergeCell ref="K59:K66"/>
-    <mergeCell ref="L58:L65"/>
-    <mergeCell ref="B67:B78"/>
-    <mergeCell ref="C67:C78"/>
-    <mergeCell ref="A79:A81"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="C79:C81"/>
-    <mergeCell ref="L79:L81"/>
-    <mergeCell ref="A82:A123"/>
-    <mergeCell ref="B82:B85"/>
-    <mergeCell ref="C82:C85"/>
-    <mergeCell ref="L82:L123"/>
-    <mergeCell ref="B86:B96"/>
-    <mergeCell ref="C86:C96"/>
-    <mergeCell ref="B97:B106"/>
-    <mergeCell ref="C97:C106"/>
-    <mergeCell ref="B107:B115"/>
-    <mergeCell ref="C107:C115"/>
-    <mergeCell ref="B116:B123"/>
-    <mergeCell ref="C116:C123"/>
-    <mergeCell ref="E126:K126"/>
-    <mergeCell ref="F127:K127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="E128:K128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="E129:K129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="E130:K130"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="E131:K131"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="E132:K132"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="E133:K133"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="E134:K134"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="E135:K135"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="E136:K136"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="E137:K137"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="E138:K138"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="E139:K139"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="E140:K140"/>
-    <mergeCell ref="B142:C142"/>
-    <mergeCell ref="E141:K141"/>
-    <mergeCell ref="B143:C143"/>
-    <mergeCell ref="E142:K142"/>
-    <mergeCell ref="B144:C144"/>
-    <mergeCell ref="E143:K143"/>
-    <mergeCell ref="B145:C145"/>
-    <mergeCell ref="E144:K144"/>
-    <mergeCell ref="B146:C146"/>
-    <mergeCell ref="E145:K145"/>
-    <mergeCell ref="B147:C147"/>
-    <mergeCell ref="E146:K146"/>
-    <mergeCell ref="B148:C148"/>
-    <mergeCell ref="E147:K147"/>
+    <mergeCell ref="A4:A55"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="L4:L6"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="C7:C12"/>
+    <mergeCell ref="L7:L12"/>
+    <mergeCell ref="B13:B21"/>
+    <mergeCell ref="C13:C21"/>
+    <mergeCell ref="L13:L21"/>
+    <mergeCell ref="B23:B35"/>
+    <mergeCell ref="C23:C35"/>
+    <mergeCell ref="L23:L35"/>
+    <mergeCell ref="B36:B39"/>
+    <mergeCell ref="C36:C39"/>
+    <mergeCell ref="L36:L38"/>
+    <mergeCell ref="L39:L51"/>
+    <mergeCell ref="B40:B51"/>
+    <mergeCell ref="C40:C51"/>
+    <mergeCell ref="B52:B55"/>
+    <mergeCell ref="C52:C55"/>
+    <mergeCell ref="L52:L55"/>
+    <mergeCell ref="A56:A77"/>
+    <mergeCell ref="B56:B65"/>
+    <mergeCell ref="C56:C65"/>
+    <mergeCell ref="L57:L64"/>
+    <mergeCell ref="D60:D67"/>
+    <mergeCell ref="E60:E67"/>
+    <mergeCell ref="F60:F67"/>
+    <mergeCell ref="G60:G67"/>
+    <mergeCell ref="H60:H67"/>
+    <mergeCell ref="I60:I67"/>
+    <mergeCell ref="J60:J67"/>
+    <mergeCell ref="K60:K67"/>
+    <mergeCell ref="B66:B77"/>
+    <mergeCell ref="C66:C77"/>
+    <mergeCell ref="A78:A80"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="C78:C80"/>
+    <mergeCell ref="L78:L80"/>
+    <mergeCell ref="A81:A122"/>
+    <mergeCell ref="B81:B84"/>
+    <mergeCell ref="C81:C84"/>
+    <mergeCell ref="L81:L122"/>
+    <mergeCell ref="B85:B95"/>
+    <mergeCell ref="C85:C95"/>
+    <mergeCell ref="B96:B105"/>
+    <mergeCell ref="C96:C105"/>
+    <mergeCell ref="B106:B114"/>
+    <mergeCell ref="C106:C114"/>
+    <mergeCell ref="B115:B122"/>
+    <mergeCell ref="C115:C122"/>
     <mergeCell ref="B149:C149"/>
-    <mergeCell ref="E148:K148"/>
-    <mergeCell ref="B150:C150"/>
-    <mergeCell ref="E149:K149"/>
-    <mergeCell ref="E392:K392"/>
+    <mergeCell ref="E301:K301"/>
+    <mergeCell ref="F302:K302"/>
+    <mergeCell ref="B301:C301"/>
+    <mergeCell ref="E303:K303"/>
+    <mergeCell ref="B302:C302"/>
+    <mergeCell ref="E304:K304"/>
+    <mergeCell ref="B303:C303"/>
+    <mergeCell ref="E305:K305"/>
+    <mergeCell ref="B304:C304"/>
+    <mergeCell ref="E306:K306"/>
+    <mergeCell ref="B305:C305"/>
+    <mergeCell ref="E307:K307"/>
+    <mergeCell ref="B306:C306"/>
+    <mergeCell ref="E308:K308"/>
+    <mergeCell ref="B307:C307"/>
+    <mergeCell ref="E309:K309"/>
+    <mergeCell ref="B308:C308"/>
+    <mergeCell ref="E310:K310"/>
+    <mergeCell ref="B309:C309"/>
+    <mergeCell ref="E311:K311"/>
+    <mergeCell ref="B310:C310"/>
+    <mergeCell ref="E312:K312"/>
+    <mergeCell ref="B311:C311"/>
+    <mergeCell ref="E313:K313"/>
+    <mergeCell ref="B312:C312"/>
+    <mergeCell ref="E314:K314"/>
+    <mergeCell ref="B313:C313"/>
+    <mergeCell ref="E315:K315"/>
+    <mergeCell ref="B314:C314"/>
+    <mergeCell ref="E316:K316"/>
+    <mergeCell ref="B315:C315"/>
+    <mergeCell ref="E317:K317"/>
+    <mergeCell ref="B316:C316"/>
+    <mergeCell ref="E318:K318"/>
+    <mergeCell ref="B317:C317"/>
+    <mergeCell ref="E319:K319"/>
+    <mergeCell ref="B318:C318"/>
+    <mergeCell ref="E320:K320"/>
+    <mergeCell ref="B319:C319"/>
+    <mergeCell ref="E321:K321"/>
+    <mergeCell ref="B320:C320"/>
+    <mergeCell ref="E322:K322"/>
+    <mergeCell ref="B321:C321"/>
+    <mergeCell ref="E323:K323"/>
+    <mergeCell ref="B322:C322"/>
+    <mergeCell ref="E324:K324"/>
+    <mergeCell ref="E393:K393"/>
+    <mergeCell ref="B392:C392"/>
+    <mergeCell ref="E394:K394"/>
     <mergeCell ref="B393:C393"/>
-    <mergeCell ref="E393:K393"/>
+    <mergeCell ref="E395:K395"/>
     <mergeCell ref="B394:C394"/>
-    <mergeCell ref="E394:K394"/>
+    <mergeCell ref="E396:K396"/>
     <mergeCell ref="B395:C395"/>
-    <mergeCell ref="E395:K395"/>
+    <mergeCell ref="E397:K397"/>
     <mergeCell ref="B396:C396"/>
-    <mergeCell ref="E396:K396"/>
+    <mergeCell ref="E398:K398"/>
     <mergeCell ref="B397:C397"/>
-    <mergeCell ref="E397:K397"/>
+    <mergeCell ref="E399:K399"/>
     <mergeCell ref="B398:C398"/>
-    <mergeCell ref="E398:K398"/>
+    <mergeCell ref="E400:K400"/>
     <mergeCell ref="B399:C399"/>
-    <mergeCell ref="E399:K399"/>
+    <mergeCell ref="E401:K401"/>
     <mergeCell ref="B400:C400"/>
-    <mergeCell ref="E400:K400"/>
+    <mergeCell ref="E402:K402"/>
     <mergeCell ref="B401:C401"/>
-    <mergeCell ref="E401:K401"/>
+    <mergeCell ref="E403:K403"/>
     <mergeCell ref="B402:C402"/>
-    <mergeCell ref="E402:K402"/>
+    <mergeCell ref="E404:K404"/>
     <mergeCell ref="B403:C403"/>
-    <mergeCell ref="E403:K403"/>
+    <mergeCell ref="E405:K405"/>
     <mergeCell ref="B404:C404"/>
-    <mergeCell ref="E404:K404"/>
+    <mergeCell ref="E406:K406"/>
     <mergeCell ref="B405:C405"/>
-    <mergeCell ref="E405:K405"/>
+    <mergeCell ref="E407:K407"/>
     <mergeCell ref="B406:C406"/>
-    <mergeCell ref="E406:K406"/>
+    <mergeCell ref="E408:K408"/>
     <mergeCell ref="B407:C407"/>
-    <mergeCell ref="E407:K407"/>
+    <mergeCell ref="E409:K409"/>
     <mergeCell ref="B408:C408"/>
-    <mergeCell ref="E408:K408"/>
+    <mergeCell ref="E410:K410"/>
     <mergeCell ref="B409:C409"/>
-    <mergeCell ref="E409:K409"/>
+    <mergeCell ref="E411:K411"/>
     <mergeCell ref="B410:C410"/>
-    <mergeCell ref="E410:K410"/>
+    <mergeCell ref="E412:K412"/>
     <mergeCell ref="B411:C411"/>
-    <mergeCell ref="E411:K411"/>
+    <mergeCell ref="E413:K413"/>
     <mergeCell ref="B412:C412"/>
-    <mergeCell ref="E412:K412"/>
+    <mergeCell ref="E414:K414"/>
     <mergeCell ref="B413:C413"/>
-    <mergeCell ref="E413:K413"/>
+    <mergeCell ref="E415:K415"/>
     <mergeCell ref="B414:C414"/>
-    <mergeCell ref="E414:K414"/>
+    <mergeCell ref="E416:K416"/>
     <mergeCell ref="B415:C415"/>
-    <mergeCell ref="E415:K415"/>
+    <mergeCell ref="E417:K417"/>
     <mergeCell ref="B416:C416"/>
-    <mergeCell ref="E416:K416"/>
+    <mergeCell ref="E418:K418"/>
     <mergeCell ref="B417:C417"/>
-    <mergeCell ref="E417:K417"/>
+    <mergeCell ref="E419:K419"/>
     <mergeCell ref="B418:C418"/>
-    <mergeCell ref="E418:K418"/>
+    <mergeCell ref="E420:K420"/>
     <mergeCell ref="B419:C419"/>
-    <mergeCell ref="E419:K419"/>
+    <mergeCell ref="E421:K421"/>
     <mergeCell ref="B420:C420"/>
-    <mergeCell ref="E420:K420"/>
+    <mergeCell ref="E422:K422"/>
     <mergeCell ref="B421:C421"/>
-    <mergeCell ref="E421:K421"/>
+    <mergeCell ref="E423:K423"/>
     <mergeCell ref="B422:C422"/>
-    <mergeCell ref="E422:K422"/>
+    <mergeCell ref="E424:K424"/>
     <mergeCell ref="B423:C423"/>
-    <mergeCell ref="E423:K423"/>
+    <mergeCell ref="E425:K425"/>
     <mergeCell ref="B424:C424"/>
-    <mergeCell ref="E424:K424"/>
+    <mergeCell ref="E426:K426"/>
     <mergeCell ref="B425:C425"/>
-    <mergeCell ref="E425:K425"/>
+    <mergeCell ref="E427:K427"/>
     <mergeCell ref="B426:C426"/>
-    <mergeCell ref="E426:K426"/>
+    <mergeCell ref="E428:K428"/>
     <mergeCell ref="B427:C427"/>
-    <mergeCell ref="E427:K427"/>
     <mergeCell ref="B428:C428"/>
     <mergeCell ref="B429:C429"/>
     <mergeCell ref="B430:C430"/>
@@ -24942,7 +24823,6 @@
     <mergeCell ref="B433:C433"/>
     <mergeCell ref="B434:C434"/>
     <mergeCell ref="B435:C435"/>
-    <mergeCell ref="B436:C436"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>

--- a/groo 산출물/groo 요구사항정의서.xlsx
+++ b/groo 산출물/groo 요구사항정의서.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.286.56066"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="440" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="430" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="정의서v3" sheetId="3" r:id="rId1"/>
@@ -14980,7 +14980,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="657">
+  <cellXfs count="656">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -16948,9 +16948,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="141">
@@ -17387,7 +17384,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U513"/>
+  <dimension ref="A1:U512"/>
   <sheetFormatPr defaultColWidth="9.00000000" defaultRowHeight="16.500000"/>
   <cols>
     <col min="1" max="1" style="311" width="22.87999916" customWidth="1" outlineLevel="0"/>
@@ -18380,7 +18377,7 @@
       <c r="N40" s="166"/>
       <c r="O40" s="166"/>
     </row>
-    <row r="41" spans="1:15" ht="17.250000" customHeight="1">
+    <row r="41" spans="1:15" ht="28.500000">
       <c r="A41" s="437"/>
       <c r="B41" s="437"/>
       <c r="C41" s="438"/>
@@ -19316,13 +19313,6 @@
         <v>0.5</v>
       </c>
       <c r="N78" s="459"/>
-      <c r="O78" s="459"/>
-      <c r="P78" s="460"/>
-      <c r="Q78" s="460"/>
-      <c r="R78" s="460"/>
-      <c r="S78" s="460"/>
-      <c r="T78" s="460"/>
-      <c r="U78" s="460"/>
     </row>
     <row r="79" spans="1:21" ht="28.500000" customHeight="1">
       <c r="A79" s="437"/>
@@ -19868,7 +19858,6 @@
         <v>170</v>
       </c>
       <c r="L103" s="437"/>
-      <c r="N103" s="460"/>
     </row>
     <row r="104" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A104" s="437"/>
@@ -20277,7 +20266,6 @@
         <v>170</v>
       </c>
       <c r="L123" s="463"/>
-      <c r="M123" s="460"/>
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="464"/>
@@ -23904,7 +23892,6 @@
       <c r="A453" s="464"/>
       <c r="B453" s="464"/>
       <c r="C453" s="464"/>
-      <c r="E453" s="463"/>
       <c r="F453" s="463"/>
       <c r="G453" s="463"/>
       <c r="H453" s="463"/>
@@ -24470,7 +24457,6 @@
       <c r="A499" s="464"/>
       <c r="B499" s="464"/>
       <c r="C499" s="464"/>
-      <c r="D499" s="311"/>
       <c r="F499" s="463"/>
       <c r="G499" s="463"/>
       <c r="H499" s="463"/>
@@ -24612,16 +24598,12 @@
       <c r="L510" s="463"/>
     </row>
     <row r="511" spans="1:12">
-      <c r="A511" s="311"/>
-      <c r="B511" s="463"/>
-      <c r="C511" s="311"/>
       <c r="F511" s="463"/>
       <c r="G511" s="463"/>
       <c r="H511" s="463"/>
       <c r="I511" s="463"/>
       <c r="J511" s="463"/>
       <c r="K511" s="463"/>
-      <c r="L511" s="311"/>
     </row>
     <row r="512" spans="1:12">
       <c r="F512" s="463"/>
@@ -24630,14 +24612,6 @@
       <c r="I512" s="463"/>
       <c r="J512" s="463"/>
       <c r="K512" s="463"/>
-    </row>
-    <row r="513">
-      <c r="F513" s="311"/>
-      <c r="G513" s="311"/>
-      <c r="H513" s="311"/>
-      <c r="I513" s="311"/>
-      <c r="J513" s="311"/>
-      <c r="K513" s="311"/>
     </row>
   </sheetData>
   <mergeCells count="182">
@@ -24697,125 +24671,125 @@
     <mergeCell ref="B115:B122"/>
     <mergeCell ref="C115:C122"/>
     <mergeCell ref="B149:C149"/>
+    <mergeCell ref="B301:C301"/>
     <mergeCell ref="E301:K301"/>
+    <mergeCell ref="B302:C302"/>
     <mergeCell ref="F302:K302"/>
-    <mergeCell ref="B301:C301"/>
+    <mergeCell ref="B303:C303"/>
     <mergeCell ref="E303:K303"/>
-    <mergeCell ref="B302:C302"/>
+    <mergeCell ref="B304:C304"/>
     <mergeCell ref="E304:K304"/>
-    <mergeCell ref="B303:C303"/>
+    <mergeCell ref="B305:C305"/>
     <mergeCell ref="E305:K305"/>
-    <mergeCell ref="B304:C304"/>
+    <mergeCell ref="B306:C306"/>
     <mergeCell ref="E306:K306"/>
-    <mergeCell ref="B305:C305"/>
+    <mergeCell ref="B307:C307"/>
     <mergeCell ref="E307:K307"/>
-    <mergeCell ref="B306:C306"/>
+    <mergeCell ref="B308:C308"/>
     <mergeCell ref="E308:K308"/>
-    <mergeCell ref="B307:C307"/>
+    <mergeCell ref="B309:C309"/>
     <mergeCell ref="E309:K309"/>
-    <mergeCell ref="B308:C308"/>
+    <mergeCell ref="B310:C310"/>
     <mergeCell ref="E310:K310"/>
-    <mergeCell ref="B309:C309"/>
+    <mergeCell ref="B311:C311"/>
     <mergeCell ref="E311:K311"/>
-    <mergeCell ref="B310:C310"/>
+    <mergeCell ref="B312:C312"/>
     <mergeCell ref="E312:K312"/>
-    <mergeCell ref="B311:C311"/>
+    <mergeCell ref="B313:C313"/>
     <mergeCell ref="E313:K313"/>
-    <mergeCell ref="B312:C312"/>
+    <mergeCell ref="B314:C314"/>
     <mergeCell ref="E314:K314"/>
-    <mergeCell ref="B313:C313"/>
+    <mergeCell ref="B315:C315"/>
     <mergeCell ref="E315:K315"/>
-    <mergeCell ref="B314:C314"/>
+    <mergeCell ref="B316:C316"/>
     <mergeCell ref="E316:K316"/>
-    <mergeCell ref="B315:C315"/>
+    <mergeCell ref="B317:C317"/>
     <mergeCell ref="E317:K317"/>
-    <mergeCell ref="B316:C316"/>
+    <mergeCell ref="B318:C318"/>
     <mergeCell ref="E318:K318"/>
-    <mergeCell ref="B317:C317"/>
+    <mergeCell ref="B319:C319"/>
     <mergeCell ref="E319:K319"/>
-    <mergeCell ref="B318:C318"/>
+    <mergeCell ref="B320:C320"/>
     <mergeCell ref="E320:K320"/>
-    <mergeCell ref="B319:C319"/>
+    <mergeCell ref="B321:C321"/>
     <mergeCell ref="E321:K321"/>
-    <mergeCell ref="B320:C320"/>
+    <mergeCell ref="B322:C322"/>
     <mergeCell ref="E322:K322"/>
-    <mergeCell ref="B321:C321"/>
     <mergeCell ref="E323:K323"/>
-    <mergeCell ref="B322:C322"/>
     <mergeCell ref="E324:K324"/>
+    <mergeCell ref="B392:C392"/>
+    <mergeCell ref="B393:C393"/>
     <mergeCell ref="E393:K393"/>
-    <mergeCell ref="B392:C392"/>
+    <mergeCell ref="B394:C394"/>
     <mergeCell ref="E394:K394"/>
-    <mergeCell ref="B393:C393"/>
+    <mergeCell ref="B395:C395"/>
     <mergeCell ref="E395:K395"/>
-    <mergeCell ref="B394:C394"/>
+    <mergeCell ref="B396:C396"/>
     <mergeCell ref="E396:K396"/>
-    <mergeCell ref="B395:C395"/>
+    <mergeCell ref="B397:C397"/>
     <mergeCell ref="E397:K397"/>
-    <mergeCell ref="B396:C396"/>
+    <mergeCell ref="B398:C398"/>
     <mergeCell ref="E398:K398"/>
-    <mergeCell ref="B397:C397"/>
+    <mergeCell ref="B399:C399"/>
     <mergeCell ref="E399:K399"/>
-    <mergeCell ref="B398:C398"/>
+    <mergeCell ref="B400:C400"/>
     <mergeCell ref="E400:K400"/>
-    <mergeCell ref="B399:C399"/>
+    <mergeCell ref="B401:C401"/>
     <mergeCell ref="E401:K401"/>
-    <mergeCell ref="B400:C400"/>
+    <mergeCell ref="B402:C402"/>
     <mergeCell ref="E402:K402"/>
-    <mergeCell ref="B401:C401"/>
+    <mergeCell ref="B403:C403"/>
     <mergeCell ref="E403:K403"/>
-    <mergeCell ref="B402:C402"/>
+    <mergeCell ref="B404:C404"/>
     <mergeCell ref="E404:K404"/>
-    <mergeCell ref="B403:C403"/>
+    <mergeCell ref="B405:C405"/>
     <mergeCell ref="E405:K405"/>
-    <mergeCell ref="B404:C404"/>
+    <mergeCell ref="B406:C406"/>
     <mergeCell ref="E406:K406"/>
-    <mergeCell ref="B405:C405"/>
+    <mergeCell ref="B407:C407"/>
     <mergeCell ref="E407:K407"/>
-    <mergeCell ref="B406:C406"/>
+    <mergeCell ref="B408:C408"/>
     <mergeCell ref="E408:K408"/>
-    <mergeCell ref="B407:C407"/>
+    <mergeCell ref="B409:C409"/>
     <mergeCell ref="E409:K409"/>
-    <mergeCell ref="B408:C408"/>
+    <mergeCell ref="B410:C410"/>
     <mergeCell ref="E410:K410"/>
-    <mergeCell ref="B409:C409"/>
+    <mergeCell ref="B411:C411"/>
     <mergeCell ref="E411:K411"/>
-    <mergeCell ref="B410:C410"/>
+    <mergeCell ref="B412:C412"/>
     <mergeCell ref="E412:K412"/>
-    <mergeCell ref="B411:C411"/>
+    <mergeCell ref="B413:C413"/>
     <mergeCell ref="E413:K413"/>
-    <mergeCell ref="B412:C412"/>
+    <mergeCell ref="B414:C414"/>
     <mergeCell ref="E414:K414"/>
-    <mergeCell ref="B413:C413"/>
+    <mergeCell ref="B415:C415"/>
     <mergeCell ref="E415:K415"/>
-    <mergeCell ref="B414:C414"/>
+    <mergeCell ref="B416:C416"/>
     <mergeCell ref="E416:K416"/>
-    <mergeCell ref="B415:C415"/>
+    <mergeCell ref="B417:C417"/>
     <mergeCell ref="E417:K417"/>
-    <mergeCell ref="B416:C416"/>
+    <mergeCell ref="B418:C418"/>
     <mergeCell ref="E418:K418"/>
-    <mergeCell ref="B417:C417"/>
+    <mergeCell ref="B419:C419"/>
     <mergeCell ref="E419:K419"/>
-    <mergeCell ref="B418:C418"/>
+    <mergeCell ref="B420:C420"/>
     <mergeCell ref="E420:K420"/>
-    <mergeCell ref="B419:C419"/>
+    <mergeCell ref="B421:C421"/>
     <mergeCell ref="E421:K421"/>
-    <mergeCell ref="B420:C420"/>
+    <mergeCell ref="B422:C422"/>
     <mergeCell ref="E422:K422"/>
-    <mergeCell ref="B421:C421"/>
+    <mergeCell ref="B423:C423"/>
     <mergeCell ref="E423:K423"/>
-    <mergeCell ref="B422:C422"/>
+    <mergeCell ref="B424:C424"/>
     <mergeCell ref="E424:K424"/>
-    <mergeCell ref="B423:C423"/>
+    <mergeCell ref="B425:C425"/>
     <mergeCell ref="E425:K425"/>
-    <mergeCell ref="B424:C424"/>
+    <mergeCell ref="B426:C426"/>
     <mergeCell ref="E426:K426"/>
-    <mergeCell ref="B425:C425"/>
+    <mergeCell ref="B427:C427"/>
     <mergeCell ref="E427:K427"/>
-    <mergeCell ref="B426:C426"/>
+    <mergeCell ref="B428:C428"/>
     <mergeCell ref="E428:K428"/>
-    <mergeCell ref="B427:C427"/>
-    <mergeCell ref="B428:C428"/>
     <mergeCell ref="B429:C429"/>
     <mergeCell ref="B430:C430"/>
     <mergeCell ref="B431:C431"/>

--- a/groo 산출물/groo 요구사항정의서.xlsx
+++ b/groo 산출물/groo 요구사항정의서.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.286.56066"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="440" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="430" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="정의서v3" sheetId="3" r:id="rId1"/>
@@ -13909,7 +13909,7 @@
       <color theme="1"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -14135,12 +14135,6 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="27">
     <border>
@@ -16724,25 +16718,25 @@
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="38" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="37" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="38" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="60" fillId="37" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="38" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="37" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="38" borderId="6" xfId="20" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="37" borderId="6" xfId="20" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="38" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="37" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="38" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="37" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="38" borderId="0" xfId="20" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="37" borderId="0" xfId="20" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="60" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -18542,7 +18536,6 @@
       <c r="L53" s="495">
         <v>0.6</v>
       </c>
-      <c r="M53" s="460"/>
     </row>
     <row r="54" spans="1:21">
       <c r="A54" s="437"/>
@@ -18563,7 +18556,6 @@
       <c r="J54" s="434"/>
       <c r="K54" s="434"/>
       <c r="L54" s="495"/>
-      <c r="M54" s="460"/>
     </row>
     <row r="55" spans="1:21" ht="270.750000" customHeight="1">
       <c r="A55" s="437"/>
@@ -18584,7 +18576,6 @@
       <c r="J55" s="434"/>
       <c r="K55" s="434"/>
       <c r="L55" s="437"/>
-      <c r="M55" s="460"/>
     </row>
     <row r="56" spans="1:21" ht="17.250000" customHeight="1">
       <c r="A56" s="437"/>
@@ -18605,7 +18596,6 @@
       <c r="J56" s="434"/>
       <c r="K56" s="434"/>
       <c r="L56" s="434"/>
-      <c r="M56" s="460"/>
     </row>
     <row r="57" spans="1:21" ht="28.500000" customHeight="1">
       <c r="A57" s="437" t="s">
@@ -18632,7 +18622,6 @@
       <c r="J57" s="434"/>
       <c r="K57" s="434"/>
       <c r="L57" s="434"/>
-      <c r="M57" s="460"/>
     </row>
     <row r="58" spans="1:21">
       <c r="A58" s="437"/>
@@ -18655,7 +18644,6 @@
       <c r="L58" s="640">
         <v>0.6</v>
       </c>
-      <c r="M58" s="460"/>
     </row>
     <row r="59" spans="1:21" ht="17.250000" customHeight="1">
       <c r="A59" s="437"/>
@@ -18676,7 +18664,6 @@
       <c r="J59" s="434"/>
       <c r="K59" s="437"/>
       <c r="L59" s="95"/>
-      <c r="M59" s="460"/>
     </row>
     <row r="60" spans="1:21" ht="17.250000" customHeight="1">
       <c r="A60" s="437"/>
@@ -18691,7 +18678,6 @@
       <c r="J60" s="434"/>
       <c r="K60" s="437"/>
       <c r="L60" s="95"/>
-      <c r="M60" s="460"/>
       <c r="N60" s="311"/>
       <c r="O60" s="463"/>
       <c r="P60" s="463"/>
@@ -18714,7 +18700,6 @@
       <c r="J61" s="434"/>
       <c r="K61" s="437"/>
       <c r="L61" s="95"/>
-      <c r="M61" s="460"/>
       <c r="N61" s="311"/>
       <c r="O61" s="463"/>
       <c r="P61" s="463"/>
@@ -18737,7 +18722,6 @@
       <c r="J62" s="434"/>
       <c r="K62" s="437"/>
       <c r="L62" s="95"/>
-      <c r="M62" s="460"/>
       <c r="N62" s="311"/>
       <c r="O62" s="463"/>
       <c r="P62" s="463"/>
@@ -18760,7 +18744,6 @@
       <c r="J63" s="434"/>
       <c r="K63" s="437"/>
       <c r="L63" s="95"/>
-      <c r="M63" s="460"/>
       <c r="N63" s="311"/>
       <c r="O63" s="463"/>
       <c r="P63" s="463"/>
@@ -18783,7 +18766,6 @@
       <c r="J64" s="434"/>
       <c r="K64" s="437"/>
       <c r="L64" s="95"/>
-      <c r="M64" s="460"/>
       <c r="N64" s="311"/>
       <c r="O64" s="463"/>
       <c r="P64" s="463"/>
@@ -18806,7 +18788,6 @@
       <c r="J65" s="434"/>
       <c r="K65" s="437"/>
       <c r="L65" s="95"/>
-      <c r="M65" s="460"/>
       <c r="N65" s="311"/>
       <c r="O65" s="463"/>
       <c r="P65" s="463"/>
@@ -18829,7 +18810,6 @@
       <c r="J66" s="434"/>
       <c r="K66" s="437"/>
       <c r="L66" s="641"/>
-      <c r="M66" s="460"/>
       <c r="N66" s="311"/>
       <c r="O66" s="463"/>
       <c r="P66" s="463"/>
@@ -18862,7 +18842,6 @@
       <c r="J67" s="295"/>
       <c r="K67" s="296"/>
       <c r="L67" s="296"/>
-      <c r="M67" s="460"/>
       <c r="N67" s="311"/>
       <c r="O67" s="463"/>
       <c r="P67" s="463"/>
@@ -19218,7 +19197,6 @@
       <c r="L79" s="495">
         <v>0.5</v>
       </c>
-      <c r="M79" s="460"/>
       <c r="N79" s="459"/>
     </row>
     <row r="80" spans="1:21" ht="28.500000" customHeight="1">
@@ -19240,7 +19218,6 @@
       <c r="J80" s="434"/>
       <c r="K80" s="434"/>
       <c r="L80" s="495"/>
-      <c r="M80" s="460"/>
       <c r="N80" s="459"/>
     </row>
     <row r="81" spans="1:14" ht="17.250000" customHeight="1">
@@ -19262,7 +19239,6 @@
       <c r="J81" s="434"/>
       <c r="K81" s="434"/>
       <c r="L81" s="437"/>
-      <c r="M81" s="460"/>
       <c r="N81" s="459"/>
     </row>
     <row r="82" spans="1:14" ht="17.250000" customHeight="1">
@@ -19292,7 +19268,6 @@
       <c r="L82" s="495">
         <v>0.3</v>
       </c>
-      <c r="M82" s="460"/>
       <c r="N82" s="459"/>
     </row>
     <row r="83" spans="1:14" ht="17.250000" customHeight="1">
@@ -19314,7 +19289,6 @@
         <v>170</v>
       </c>
       <c r="L83" s="437"/>
-      <c r="M83" s="460"/>
       <c r="N83" s="459"/>
     </row>
     <row r="84" spans="1:14" ht="17.250000" customHeight="1">
@@ -19336,7 +19310,6 @@
         <v>170</v>
       </c>
       <c r="L84" s="437"/>
-      <c r="M84" s="460"/>
       <c r="N84" s="459"/>
     </row>
     <row r="85" spans="1:14" ht="17.250000" customHeight="1">
@@ -19358,7 +19331,6 @@
         <v>170</v>
       </c>
       <c r="L85" s="437"/>
-      <c r="M85" s="460"/>
       <c r="N85" s="459"/>
     </row>
     <row r="86" spans="1:14" ht="17.250000" customHeight="1">
@@ -19384,7 +19356,6 @@
         <v>170</v>
       </c>
       <c r="L86" s="437"/>
-      <c r="M86" s="460"/>
       <c r="N86" s="459"/>
     </row>
     <row r="87" spans="1:14" ht="17.250000" customHeight="1">
@@ -19406,7 +19377,6 @@
         <v>170</v>
       </c>
       <c r="L87" s="437"/>
-      <c r="M87" s="460"/>
       <c r="N87" s="459"/>
     </row>
     <row r="88" spans="1:14" ht="17.250000" customHeight="1">
@@ -19428,7 +19398,6 @@
         <v>170</v>
       </c>
       <c r="L88" s="437"/>
-      <c r="M88" s="460"/>
       <c r="N88" s="459"/>
     </row>
     <row r="89" spans="1:14" ht="17.250000" customHeight="1">
@@ -19450,7 +19419,6 @@
         <v>170</v>
       </c>
       <c r="L89" s="437"/>
-      <c r="M89" s="460"/>
       <c r="N89" s="459"/>
     </row>
     <row r="90" spans="1:14" ht="17.250000" customHeight="1">
@@ -19472,7 +19440,6 @@
         <v>170</v>
       </c>
       <c r="L90" s="437"/>
-      <c r="M90" s="460"/>
       <c r="N90" s="459"/>
     </row>
     <row r="91" spans="1:14" ht="17.250000" customHeight="1">
@@ -19494,7 +19461,6 @@
         <v>170</v>
       </c>
       <c r="L91" s="437"/>
-      <c r="M91" s="460"/>
       <c r="N91" s="459"/>
     </row>
     <row r="92" spans="1:14" ht="17.250000" customHeight="1">
@@ -19516,7 +19482,6 @@
         <v>170</v>
       </c>
       <c r="L92" s="437"/>
-      <c r="M92" s="460"/>
       <c r="N92" s="459"/>
     </row>
     <row r="93" spans="1:14" ht="17.250000" customHeight="1">
@@ -19538,7 +19503,6 @@
         <v>170</v>
       </c>
       <c r="L93" s="437"/>
-      <c r="M93" s="460"/>
       <c r="N93" s="459"/>
     </row>
     <row r="94" spans="1:14" ht="17.250000" customHeight="1">
@@ -19560,7 +19524,6 @@
         <v>170</v>
       </c>
       <c r="L94" s="437"/>
-      <c r="M94" s="460"/>
       <c r="N94" s="459"/>
     </row>
     <row r="95" spans="1:14" ht="17.250000" customHeight="1">
@@ -19582,7 +19545,6 @@
         <v>170</v>
       </c>
       <c r="L95" s="437"/>
-      <c r="M95" s="460"/>
       <c r="N95" s="459"/>
     </row>
     <row r="96" spans="1:14" ht="17.250000" customHeight="1">
@@ -19604,7 +19566,6 @@
         <v>170</v>
       </c>
       <c r="L96" s="437"/>
-      <c r="M96" s="460"/>
       <c r="N96" s="459"/>
     </row>
     <row r="97" spans="1:14" ht="17.250000" customHeight="1">
@@ -19630,7 +19591,6 @@
         <v>170</v>
       </c>
       <c r="L97" s="437"/>
-      <c r="M97" s="460"/>
       <c r="N97" s="459"/>
     </row>
     <row r="98" spans="1:14" ht="17.250000" customHeight="1">
@@ -19652,7 +19612,6 @@
         <v>170</v>
       </c>
       <c r="L98" s="437"/>
-      <c r="M98" s="460"/>
       <c r="N98" s="459"/>
     </row>
     <row r="99" spans="1:14" ht="17.250000" customHeight="1">
@@ -19784,8 +19743,6 @@
         <v>170</v>
       </c>
       <c r="L104" s="437"/>
-      <c r="M104" s="460"/>
-      <c r="N104" s="460"/>
     </row>
     <row r="105" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A105" s="437"/>
@@ -19806,7 +19763,6 @@
         <v>170</v>
       </c>
       <c r="L105" s="437"/>
-      <c r="M105" s="460"/>
     </row>
     <row r="106" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A106" s="437"/>
@@ -19827,7 +19783,6 @@
         <v>170</v>
       </c>
       <c r="L106" s="437"/>
-      <c r="M106" s="460"/>
     </row>
     <row r="107" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A107" s="437"/>
@@ -19852,7 +19807,6 @@
         <v>170</v>
       </c>
       <c r="L107" s="437"/>
-      <c r="M107" s="460"/>
     </row>
     <row r="108" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A108" s="437"/>
@@ -19873,7 +19827,6 @@
         <v>170</v>
       </c>
       <c r="L108" s="437"/>
-      <c r="M108" s="460"/>
     </row>
     <row r="109" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A109" s="437"/>
@@ -19894,7 +19847,6 @@
         <v>170</v>
       </c>
       <c r="L109" s="437"/>
-      <c r="M109" s="460"/>
     </row>
     <row r="110" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A110" s="437"/>
@@ -19915,7 +19867,6 @@
         <v>170</v>
       </c>
       <c r="L110" s="437"/>
-      <c r="M110" s="460"/>
     </row>
     <row r="111" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A111" s="437"/>
@@ -19936,7 +19887,6 @@
         <v>170</v>
       </c>
       <c r="L111" s="437"/>
-      <c r="M111" s="460"/>
     </row>
     <row r="112" spans="1:14" ht="17.250000" customHeight="1">
       <c r="A112" s="437"/>
@@ -19957,7 +19907,6 @@
         <v>170</v>
       </c>
       <c r="L112" s="437"/>
-      <c r="M112" s="460"/>
     </row>
     <row r="113" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A113" s="437"/>
@@ -19978,7 +19927,6 @@
         <v>170</v>
       </c>
       <c r="L113" s="437"/>
-      <c r="M113" s="460"/>
     </row>
     <row r="114" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A114" s="437"/>
@@ -19999,7 +19947,6 @@
         <v>170</v>
       </c>
       <c r="L114" s="437"/>
-      <c r="M114" s="460"/>
     </row>
     <row r="115" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A115" s="437"/>
@@ -20020,7 +19967,6 @@
         <v>170</v>
       </c>
       <c r="L115" s="437"/>
-      <c r="M115" s="460"/>
     </row>
     <row r="116" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A116" s="437"/>
@@ -20045,7 +19991,6 @@
         <v>170</v>
       </c>
       <c r="L116" s="437"/>
-      <c r="M116" s="460"/>
     </row>
     <row r="117" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A117" s="437"/>
@@ -20066,7 +20011,6 @@
         <v>170</v>
       </c>
       <c r="L117" s="437"/>
-      <c r="M117" s="460"/>
     </row>
     <row r="118" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A118" s="437"/>
@@ -20087,7 +20031,6 @@
         <v>170</v>
       </c>
       <c r="L118" s="437"/>
-      <c r="M118" s="460"/>
     </row>
     <row r="119" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A119" s="437"/>
@@ -20108,7 +20051,6 @@
         <v>170</v>
       </c>
       <c r="L119" s="437"/>
-      <c r="M119" s="460"/>
     </row>
     <row r="120" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A120" s="437"/>
@@ -20129,7 +20071,6 @@
         <v>170</v>
       </c>
       <c r="L120" s="437"/>
-      <c r="M120" s="460"/>
     </row>
     <row r="121" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A121" s="437"/>
@@ -20150,7 +20091,6 @@
         <v>170</v>
       </c>
       <c r="L121" s="437"/>
-      <c r="M121" s="460"/>
     </row>
     <row r="122" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A122" s="437"/>
@@ -20171,7 +20111,6 @@
         <v>170</v>
       </c>
       <c r="L122" s="437"/>
-      <c r="M122" s="460"/>
     </row>
     <row r="123" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A123" s="434"/>
@@ -20196,10 +20135,7 @@
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="463"/>
-      <c r="B124" s="463"/>
       <c r="C124" s="463"/>
-      <c r="D124" s="311"/>
-      <c r="E124" s="463"/>
       <c r="F124" s="463"/>
       <c r="G124" s="463"/>
       <c r="H124" s="463"/>
@@ -20207,7 +20143,6 @@
       <c r="J124" s="463"/>
       <c r="K124" s="463"/>
       <c r="L124" s="463"/>
-      <c r="M124" s="460"/>
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="464"/>
@@ -20258,7 +20193,6 @@
       <c r="J127" s="441"/>
       <c r="K127" s="492"/>
       <c r="L127" s="442"/>
-      <c r="M127" s="460"/>
     </row>
     <row r="128" spans="1:13" ht="40.200000" customHeight="1">
       <c r="A128" s="80" t="s">
@@ -22974,7 +22908,7 @@
       <c r="K352" s="463"/>
       <c r="L352" s="463"/>
     </row>
-    <row r="353" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="353" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A353" s="463"/>
       <c r="C353" s="463"/>
       <c r="F353" s="463"/>
@@ -22985,7 +22919,7 @@
       <c r="K353" s="463"/>
       <c r="L353" s="463"/>
     </row>
-    <row r="354" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="354" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A354" s="463"/>
       <c r="C354" s="463"/>
       <c r="F354" s="463"/>
@@ -22996,7 +22930,7 @@
       <c r="K354" s="463"/>
       <c r="L354" s="463"/>
     </row>
-    <row r="355" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="355" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A355" s="463"/>
       <c r="C355" s="463"/>
       <c r="F355" s="463"/>
@@ -23007,7 +22941,7 @@
       <c r="K355" s="463"/>
       <c r="L355" s="463"/>
     </row>
-    <row r="356" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="356" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A356" s="463"/>
       <c r="C356" s="463"/>
       <c r="F356" s="463"/>
@@ -23018,7 +22952,7 @@
       <c r="K356" s="463"/>
       <c r="L356" s="463"/>
     </row>
-    <row r="357" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="357" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A357" s="463"/>
       <c r="C357" s="463"/>
       <c r="F357" s="463"/>
@@ -23029,7 +22963,7 @@
       <c r="K357" s="463"/>
       <c r="L357" s="463"/>
     </row>
-    <row r="358" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="358" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A358" s="463"/>
       <c r="C358" s="463"/>
       <c r="F358" s="463"/>
@@ -23040,7 +22974,7 @@
       <c r="K358" s="463"/>
       <c r="L358" s="463"/>
     </row>
-    <row r="359" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="359" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A359" s="463"/>
       <c r="C359" s="463"/>
       <c r="F359" s="463"/>
@@ -23051,7 +22985,7 @@
       <c r="K359" s="463"/>
       <c r="L359" s="463"/>
     </row>
-    <row r="360" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="360" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A360" s="463"/>
       <c r="C360" s="463"/>
       <c r="F360" s="463"/>
@@ -23062,7 +22996,7 @@
       <c r="K360" s="463"/>
       <c r="L360" s="463"/>
     </row>
-    <row r="361" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="361" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A361" s="463"/>
       <c r="C361" s="463"/>
       <c r="F361" s="463"/>
@@ -23073,7 +23007,7 @@
       <c r="K361" s="463"/>
       <c r="L361" s="463"/>
     </row>
-    <row r="362" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="362" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A362" s="463"/>
       <c r="C362" s="463"/>
       <c r="F362" s="463"/>
@@ -23084,7 +23018,7 @@
       <c r="K362" s="463"/>
       <c r="L362" s="463"/>
     </row>
-    <row r="363" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="363" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A363" s="463"/>
       <c r="C363" s="463"/>
       <c r="F363" s="463"/>
@@ -23095,7 +23029,7 @@
       <c r="K363" s="463"/>
       <c r="L363" s="463"/>
     </row>
-    <row r="364" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="364" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A364" s="463"/>
       <c r="C364" s="463"/>
       <c r="F364" s="463"/>
@@ -23106,112 +23040,92 @@
       <c r="K364" s="463"/>
       <c r="L364" s="463"/>
     </row>
-    <row r="365" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="365" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A365" s="463"/>
       <c r="C365" s="463"/>
-      <c r="D365" s="311"/>
       <c r="L365" s="463"/>
     </row>
-    <row r="366" spans="1:13" ht="17.250000" customHeight="1">
-      <c r="D366" s="311"/>
+    <row r="366" spans="1:12" ht="17.250000" customHeight="1">
       <c r="L366" s="463"/>
     </row>
-    <row r="367" spans="1:13" ht="17.250000" customHeight="1">
+    <row r="367" spans="1:12" ht="17.250000" customHeight="1">
       <c r="L367" s="463"/>
-      <c r="M367" s="460"/>
-    </row>
-    <row r="368" spans="1:13" ht="17.250000" customHeight="1">
+    </row>
+    <row r="368" spans="1:12" ht="17.250000" customHeight="1">
       <c r="L368" s="463"/>
-      <c r="M368" s="460"/>
-    </row>
-    <row r="369" spans="2:13" ht="17.250000" customHeight="1">
+    </row>
+    <row r="369" spans="2:12" ht="17.250000" customHeight="1">
       <c r="L369" s="507"/>
-      <c r="M369" s="460"/>
-    </row>
-    <row r="370" spans="2:13" ht="17.250000" customHeight="1">
+    </row>
+    <row r="370" spans="2:12" ht="17.250000" customHeight="1">
       <c r="B370" s="311"/>
-      <c r="C370" s="311"/>
       <c r="L370" s="464"/>
     </row>
-    <row r="371" spans="2:13">
+    <row r="371" spans="2:12">
       <c r="B371" s="311"/>
-      <c r="C371" s="311"/>
-    </row>
-    <row r="373" spans="2:13">
+    </row>
+    <row r="373" spans="2:12">
       <c r="L373" s="511"/>
     </row>
-    <row r="374" spans="2:13" ht="54.000000" customHeight="1">
+    <row r="374" spans="2:12" ht="54.000000" customHeight="1">
       <c r="B374" s="311"/>
-      <c r="C374" s="311"/>
       <c r="L374" s="511"/>
     </row>
-    <row r="375" spans="2:13" ht="42.750000" customHeight="1">
+    <row r="375" spans="2:12" ht="42.750000" customHeight="1">
       <c r="B375" s="311"/>
-      <c r="C375" s="311"/>
       <c r="L375" s="551"/>
     </row>
-    <row r="376" spans="2:13" ht="42.750000">
+    <row r="376" spans="2:12" ht="42.750000">
       <c r="L376" s="551"/>
     </row>
-    <row r="377" spans="2:13" ht="57.000000">
+    <row r="377" spans="2:12" ht="57.000000">
       <c r="B377" s="311"/>
-      <c r="C377" s="311"/>
       <c r="L377" s="551"/>
     </row>
-    <row r="378" spans="2:13" ht="57.000000">
+    <row r="378" spans="2:12" ht="57.000000">
       <c r="B378" s="311"/>
-      <c r="C378" s="311"/>
       <c r="L378" s="551"/>
     </row>
-    <row r="379" spans="2:13" ht="42.750000">
+    <row r="379" spans="2:12" ht="42.750000">
       <c r="B379" s="311"/>
-      <c r="C379" s="311"/>
       <c r="L379" s="551"/>
     </row>
-    <row r="380" spans="2:13" ht="42.750000">
+    <row r="380" spans="2:12" ht="42.750000">
       <c r="B380" s="311"/>
-      <c r="C380" s="311"/>
       <c r="L380" s="551"/>
     </row>
-    <row r="381" spans="2:13" ht="42.750000">
+    <row r="381" spans="2:12" ht="42.750000">
       <c r="B381" s="311"/>
-      <c r="C381" s="311"/>
       <c r="L381" s="551"/>
     </row>
-    <row r="382" spans="2:13" ht="42.750000">
+    <row r="382" spans="2:12" ht="42.750000">
       <c r="L382" s="551"/>
     </row>
-    <row r="383" spans="2:13" ht="42.750000">
+    <row r="383" spans="2:12" ht="42.750000">
       <c r="B383" s="311"/>
-      <c r="C383" s="311"/>
       <c r="L383" s="551"/>
     </row>
-    <row r="384" spans="2:13" ht="42.750000">
+    <row r="384" spans="2:12" ht="42.750000">
       <c r="L384" s="551"/>
     </row>
     <row r="385" spans="1:12" ht="28.500000">
       <c r="B385" s="311"/>
-      <c r="C385" s="311"/>
       <c r="L385" s="551"/>
     </row>
     <row r="386" spans="1:12" ht="42.750000">
       <c r="B386" s="311"/>
-      <c r="C386" s="311"/>
       <c r="L386" s="551"/>
     </row>
     <row r="387" spans="1:12" ht="42.750000">
       <c r="B387" s="311"/>
-      <c r="C387" s="311"/>
       <c r="L387" s="551"/>
     </row>
     <row r="388" spans="1:12" ht="42.750000">
       <c r="B388" s="311"/>
-      <c r="C388" s="311"/>
       <c r="L388" s="551"/>
     </row>
     <row r="389" spans="1:12" ht="42.750000">
       <c r="B389" s="311"/>
-      <c r="C389" s="311"/>
       <c r="L389" s="551"/>
     </row>
     <row r="390" spans="1:12">
@@ -23219,7 +23133,6 @@
     </row>
     <row r="391" spans="1:12">
       <c r="B391" s="311"/>
-      <c r="C391" s="311"/>
       <c r="L391" s="551"/>
     </row>
     <row r="392" spans="1:12" ht="17.250000" customHeight="1">
@@ -24016,7 +23929,6 @@
       <c r="A452" s="464"/>
       <c r="B452" s="464"/>
       <c r="C452" s="464"/>
-      <c r="E452" s="463"/>
       <c r="F452" s="463"/>
       <c r="G452" s="463"/>
       <c r="H452" s="463"/>
@@ -24582,7 +24494,6 @@
       <c r="A498" s="464"/>
       <c r="B498" s="464"/>
       <c r="C498" s="464"/>
-      <c r="D498" s="311"/>
       <c r="F498" s="463"/>
       <c r="G498" s="463"/>
       <c r="H498" s="463"/>
@@ -24746,18 +24657,6 @@
       <c r="J511" s="463"/>
       <c r="K511" s="463"/>
       <c r="L511" s="463"/>
-    </row>
-    <row r="512" spans="1:12">
-      <c r="A512" s="311"/>
-      <c r="B512" s="463"/>
-      <c r="C512" s="311"/>
-      <c r="F512" s="311"/>
-      <c r="G512" s="311"/>
-      <c r="H512" s="311"/>
-      <c r="I512" s="311"/>
-      <c r="J512" s="311"/>
-      <c r="K512" s="311"/>
-      <c r="L512" s="311"/>
     </row>
   </sheetData>
   <mergeCells count="182">
@@ -24789,6 +24688,7 @@
     <mergeCell ref="A57:A78"/>
     <mergeCell ref="B57:B66"/>
     <mergeCell ref="C57:C66"/>
+    <mergeCell ref="L58:L65"/>
     <mergeCell ref="D59:D66"/>
     <mergeCell ref="E59:E66"/>
     <mergeCell ref="F59:F66"/>
@@ -24797,7 +24697,6 @@
     <mergeCell ref="I59:I66"/>
     <mergeCell ref="J59:J66"/>
     <mergeCell ref="K59:K66"/>
-    <mergeCell ref="L58:L65"/>
     <mergeCell ref="B67:B78"/>
     <mergeCell ref="C67:C78"/>
     <mergeCell ref="A79:A81"/>
@@ -24823,46 +24722,46 @@
     <mergeCell ref="B129:C129"/>
     <mergeCell ref="E129:K129"/>
     <mergeCell ref="B130:C130"/>
+    <mergeCell ref="E130:K130"/>
     <mergeCell ref="B131:C131"/>
-    <mergeCell ref="E130:K130"/>
+    <mergeCell ref="E131:K131"/>
     <mergeCell ref="B132:C132"/>
-    <mergeCell ref="E131:K131"/>
+    <mergeCell ref="E132:K132"/>
     <mergeCell ref="B133:C133"/>
-    <mergeCell ref="E132:K132"/>
+    <mergeCell ref="E133:K133"/>
     <mergeCell ref="B134:C134"/>
-    <mergeCell ref="E133:K133"/>
+    <mergeCell ref="E134:K134"/>
     <mergeCell ref="B135:C135"/>
-    <mergeCell ref="E134:K134"/>
+    <mergeCell ref="E135:K135"/>
     <mergeCell ref="B136:C136"/>
-    <mergeCell ref="E135:K135"/>
+    <mergeCell ref="E136:K136"/>
     <mergeCell ref="B137:C137"/>
-    <mergeCell ref="E136:K136"/>
+    <mergeCell ref="E137:K137"/>
     <mergeCell ref="B138:C138"/>
-    <mergeCell ref="E137:K137"/>
+    <mergeCell ref="E138:K138"/>
     <mergeCell ref="B139:C139"/>
-    <mergeCell ref="E138:K138"/>
+    <mergeCell ref="E139:K139"/>
     <mergeCell ref="B140:C140"/>
-    <mergeCell ref="E139:K139"/>
+    <mergeCell ref="E140:K140"/>
     <mergeCell ref="B141:C141"/>
-    <mergeCell ref="E140:K140"/>
+    <mergeCell ref="E141:K141"/>
     <mergeCell ref="B142:C142"/>
-    <mergeCell ref="E141:K141"/>
+    <mergeCell ref="E142:K142"/>
     <mergeCell ref="B143:C143"/>
-    <mergeCell ref="E142:K142"/>
+    <mergeCell ref="E143:K143"/>
     <mergeCell ref="B144:C144"/>
-    <mergeCell ref="E143:K143"/>
+    <mergeCell ref="E144:K144"/>
     <mergeCell ref="B145:C145"/>
-    <mergeCell ref="E144:K144"/>
+    <mergeCell ref="E145:K145"/>
     <mergeCell ref="B146:C146"/>
-    <mergeCell ref="E145:K145"/>
+    <mergeCell ref="E146:K146"/>
     <mergeCell ref="B147:C147"/>
-    <mergeCell ref="E146:K146"/>
+    <mergeCell ref="E147:K147"/>
     <mergeCell ref="B148:C148"/>
-    <mergeCell ref="E147:K147"/>
+    <mergeCell ref="E148:K148"/>
     <mergeCell ref="B149:C149"/>
-    <mergeCell ref="E148:K148"/>
+    <mergeCell ref="E149:K149"/>
     <mergeCell ref="B150:C150"/>
-    <mergeCell ref="E149:K149"/>
     <mergeCell ref="E392:K392"/>
     <mergeCell ref="B393:C393"/>
     <mergeCell ref="E393:K393"/>

--- a/groo 산출물/groo 요구사항정의서.xlsx
+++ b/groo 산출물/groo 요구사항정의서.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.286.56066"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="430" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="420" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="정의서v3" sheetId="3" r:id="rId1"/>
@@ -17243,7 +17243,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U512"/>
+  <dimension ref="A1:U511"/>
   <sheetFormatPr defaultColWidth="9.00000000" defaultRowHeight="16.500000"/>
   <cols>
     <col min="1" max="1" style="311" width="22.87999916" customWidth="1" outlineLevel="0"/>

--- a/groo 산출물/groo 요구사항정의서.xlsx
+++ b/groo 산출물/groo 요구사항정의서.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.286.56066"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="420" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="410" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="정의서v3" sheetId="3" r:id="rId1"/>

--- a/groo 산출물/groo 요구사항정의서.xlsx
+++ b/groo 산출물/groo 요구사항정의서.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.286.56066"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="410" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="400" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="정의서v3" sheetId="3" r:id="rId1"/>
